--- a/research/traditional_assets/database/data/morocco/morocco_telecom_services.xlsx
+++ b/research/traditional_assets/database/data/morocco/morocco_telecom_services.xlsx
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.08667580553052057</v>
+        <v>0.0864290429528229</v>
       </c>
       <c r="C2">
-        <v>8543.501447387995</v>
+        <v>8480.25298396407</v>
       </c>
       <c r="D2">
-        <v>8441.201447387995</v>
+        <v>8464.549983964071</v>
       </c>
       <c r="E2">
-        <v>-1547.8</v>
+        <v>-1461.203</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>86.59699999999999</v>
       </c>
       <c r="G2">
         <v>102.3</v>
@@ -1451,28 +1451,28 @@
         <v>336.1000000000001</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>4.355829099999999</v>
       </c>
       <c r="N2">
-        <v>336.1000000000001</v>
+        <v>331.7441709000001</v>
       </c>
       <c r="O2">
-        <v>107.552</v>
+        <v>106.158134688</v>
       </c>
       <c r="P2">
-        <v>228.5480000000001</v>
+        <v>225.5860362120001</v>
       </c>
       <c r="Q2">
-        <v>1608.348</v>
+        <v>1605.386036212</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.08667580553052057</v>
+        <v>0.08695656863921505</v>
       </c>
       <c r="T2">
-        <v>0.532748774085323</v>
+        <v>0.5364080585941918</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>77.16097034201829</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.0864290429528229</v>
+        <v>0.08618228037512524</v>
       </c>
       <c r="C3">
-        <v>8480.25298396407</v>
+        <v>8417.134043867773</v>
       </c>
       <c r="D3">
-        <v>8464.549983964071</v>
+        <v>8488.028043867773</v>
       </c>
       <c r="E3">
-        <v>-1461.203</v>
+        <v>-1374.606</v>
       </c>
       <c r="F3">
-        <v>86.59699999999999</v>
+        <v>173.194</v>
       </c>
       <c r="G3">
         <v>102.3</v>
@@ -1533,28 +1533,28 @@
         <v>336.1000000000001</v>
       </c>
       <c r="M3">
-        <v>4.355829099999999</v>
+        <v>8.711658199999999</v>
       </c>
       <c r="N3">
-        <v>331.7441709000001</v>
+        <v>327.3883418000001</v>
       </c>
       <c r="O3">
-        <v>106.158134688</v>
+        <v>104.764269376</v>
       </c>
       <c r="P3">
-        <v>225.5860362120001</v>
+        <v>222.6240724240001</v>
       </c>
       <c r="Q3">
-        <v>1605.386036212</v>
+        <v>1602.424072424</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.08695656863921505</v>
+        <v>0.08724306160727065</v>
       </c>
       <c r="T3">
-        <v>0.5364080585941918</v>
+        <v>0.5401420223787519</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>77.16097034201829</v>
+        <v>38.58048517100914</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.08618228037512524</v>
+        <v>0.08593551779742757</v>
       </c>
       <c r="C4">
-        <v>8417.134043867773</v>
+        <v>8354.145707870528</v>
       </c>
       <c r="D4">
-        <v>8488.028043867773</v>
+        <v>8511.636707870528</v>
       </c>
       <c r="E4">
-        <v>-1374.606</v>
+        <v>-1288.009</v>
       </c>
       <c r="F4">
-        <v>173.194</v>
+        <v>259.7909999999999</v>
       </c>
       <c r="G4">
         <v>102.3</v>
@@ -1615,28 +1615,28 @@
         <v>336.1000000000001</v>
       </c>
       <c r="M4">
-        <v>8.711658199999999</v>
+        <v>13.0674873</v>
       </c>
       <c r="N4">
-        <v>327.3883418000001</v>
+        <v>323.0325127000002</v>
       </c>
       <c r="O4">
-        <v>104.764269376</v>
+        <v>103.3704040640001</v>
       </c>
       <c r="P4">
-        <v>222.6240724240001</v>
+        <v>219.6621086360001</v>
       </c>
       <c r="Q4">
-        <v>1602.424072424</v>
+        <v>1599.462108636</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.08724306160727065</v>
+        <v>0.08753546164683254</v>
       </c>
       <c r="T4">
-        <v>0.5401420223787519</v>
+        <v>0.5439529751073235</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>38.58048517100914</v>
+        <v>25.72032344733943</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.08593551779742757</v>
+        <v>0.08568875521972989</v>
       </c>
       <c r="C5">
-        <v>8354.145707870528</v>
+        <v>8291.289068801561</v>
       </c>
       <c r="D5">
-        <v>8511.636707870528</v>
+        <v>8535.377068801563</v>
       </c>
       <c r="E5">
-        <v>-1288.009</v>
+        <v>-1201.412</v>
       </c>
       <c r="F5">
-        <v>259.7909999999999</v>
+        <v>346.388</v>
       </c>
       <c r="G5">
         <v>102.3</v>
@@ -1697,28 +1697,28 @@
         <v>336.1000000000001</v>
       </c>
       <c r="M5">
-        <v>13.0674873</v>
+        <v>17.4233164</v>
       </c>
       <c r="N5">
-        <v>323.0325127000002</v>
+        <v>318.6766836000002</v>
       </c>
       <c r="O5">
-        <v>103.3704040640001</v>
+        <v>101.9765387520001</v>
       </c>
       <c r="P5">
-        <v>219.6621086360001</v>
+        <v>216.7001448480001</v>
       </c>
       <c r="Q5">
-        <v>1599.462108636</v>
+        <v>1596.500144848</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.08753546164683254</v>
+        <v>0.08783395335388532</v>
       </c>
       <c r="T5">
-        <v>0.5439529751073235</v>
+        <v>0.5478433226844071</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>25.72032344733943</v>
+        <v>19.29024258550457</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.08568875521972989</v>
+        <v>0.08544199264203224</v>
       </c>
       <c r="C6">
-        <v>8291.289068801561</v>
+        <v>8228.565231716526</v>
       </c>
       <c r="D6">
-        <v>8535.377068801563</v>
+        <v>8559.250231716527</v>
       </c>
       <c r="E6">
-        <v>-1201.412</v>
+        <v>-1114.815</v>
       </c>
       <c r="F6">
-        <v>346.388</v>
+        <v>432.985</v>
       </c>
       <c r="G6">
         <v>102.3</v>
@@ -1779,28 +1779,28 @@
         <v>336.1000000000001</v>
       </c>
       <c r="M6">
-        <v>17.4233164</v>
+        <v>21.7791455</v>
       </c>
       <c r="N6">
-        <v>318.6766836000002</v>
+        <v>314.3208545000001</v>
       </c>
       <c r="O6">
-        <v>101.9765387520001</v>
+        <v>100.58267344</v>
       </c>
       <c r="P6">
-        <v>216.7001448480001</v>
+        <v>213.7381810600001</v>
       </c>
       <c r="Q6">
-        <v>1596.500144848</v>
+        <v>1593.53818106</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.08783395335388532</v>
+        <v>0.08813872909687605</v>
       </c>
       <c r="T6">
-        <v>0.5478433226844071</v>
+        <v>0.5518155723157451</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>19.29024258550457</v>
+        <v>15.43219406840365</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.08544199264203224</v>
+        <v>0.08519523006433456</v>
       </c>
       <c r="C7">
-        <v>8228.565231716526</v>
+        <v>8165.975314068966</v>
       </c>
       <c r="D7">
-        <v>8559.250231716527</v>
+        <v>8583.257314068967</v>
       </c>
       <c r="E7">
-        <v>-1114.815</v>
+        <v>-1028.218</v>
       </c>
       <c r="F7">
-        <v>432.985</v>
+        <v>519.582</v>
       </c>
       <c r="G7">
         <v>102.3</v>
@@ -1861,28 +1861,28 @@
         <v>336.1000000000001</v>
       </c>
       <c r="M7">
-        <v>21.7791455</v>
+        <v>26.1349746</v>
       </c>
       <c r="N7">
-        <v>314.3208545000001</v>
+        <v>309.9650254000001</v>
       </c>
       <c r="O7">
-        <v>100.58267344</v>
+        <v>99.18880812800003</v>
       </c>
       <c r="P7">
-        <v>213.7381810600001</v>
+        <v>210.7762172720001</v>
       </c>
       <c r="Q7">
-        <v>1593.53818106</v>
+        <v>1590.576217272</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.08813872909687605</v>
+        <v>0.08844998943014316</v>
       </c>
       <c r="T7">
-        <v>0.5518155723157451</v>
+        <v>0.5558723378966859</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>15.43219406840365</v>
+        <v>12.86016172366971</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.08519523006433456</v>
+        <v>0.08494846748663691</v>
       </c>
       <c r="C8">
-        <v>8165.975314068966</v>
+        <v>8103.520445884666</v>
       </c>
       <c r="D8">
-        <v>8583.257314068967</v>
+        <v>8607.399445884666</v>
       </c>
       <c r="E8">
-        <v>-1028.218</v>
+        <v>-941.6210000000001</v>
       </c>
       <c r="F8">
-        <v>519.5819999999999</v>
+        <v>606.1789999999999</v>
       </c>
       <c r="G8">
         <v>102.3</v>
@@ -1943,28 +1943,28 @@
         <v>336.1000000000001</v>
       </c>
       <c r="M8">
-        <v>26.13497459999999</v>
+        <v>30.49080369999999</v>
       </c>
       <c r="N8">
-        <v>309.9650254000002</v>
+        <v>305.6091963000001</v>
       </c>
       <c r="O8">
-        <v>99.18880812800006</v>
+        <v>97.79494281600005</v>
       </c>
       <c r="P8">
-        <v>210.7762172720001</v>
+        <v>207.8142534840001</v>
       </c>
       <c r="Q8">
-        <v>1590.576217272</v>
+        <v>1587.614253484</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.08844998943014316</v>
+        <v>0.08876794353401818</v>
       </c>
       <c r="T8">
-        <v>0.5558723378966859</v>
+        <v>0.5600163457481847</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>12.86016172366972</v>
+        <v>11.02299576314547</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.0849484674866369</v>
+        <v>0.08470170490893926</v>
       </c>
       <c r="C9">
-        <v>8103.520445884667</v>
+        <v>8041.201769938982</v>
       </c>
       <c r="D9">
-        <v>8607.399445884668</v>
+        <v>8631.677769938982</v>
       </c>
       <c r="E9">
-        <v>-941.621</v>
+        <v>-855.024</v>
       </c>
       <c r="F9">
-        <v>606.179</v>
+        <v>692.776</v>
       </c>
       <c r="G9">
         <v>102.3</v>
@@ -2025,28 +2025,28 @@
         <v>336.1000000000001</v>
       </c>
       <c r="M9">
-        <v>30.4908037</v>
+        <v>34.84663279999999</v>
       </c>
       <c r="N9">
-        <v>305.6091963000001</v>
+        <v>301.2533672000001</v>
       </c>
       <c r="O9">
-        <v>97.79494281600005</v>
+        <v>96.40107750400004</v>
       </c>
       <c r="P9">
-        <v>207.8142534840001</v>
+        <v>204.8522896960001</v>
       </c>
       <c r="Q9">
-        <v>1587.614253484</v>
+        <v>1584.652289696</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.08876794353401818</v>
+        <v>0.08909280968362962</v>
       </c>
       <c r="T9">
-        <v>0.5600163457481847</v>
+        <v>0.5642504407268899</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>11.02299576314547</v>
+        <v>9.645121292752284</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.08470170490893926</v>
+        <v>0.0845467423312416</v>
       </c>
       <c r="C10">
-        <v>8041.201769938982</v>
+        <v>7969.921266958636</v>
       </c>
       <c r="D10">
-        <v>8631.677769938982</v>
+        <v>8646.994266958636</v>
       </c>
       <c r="E10">
-        <v>-855.024</v>
+        <v>-768.4270000000001</v>
       </c>
       <c r="F10">
-        <v>692.776</v>
+        <v>779.3729999999998</v>
       </c>
       <c r="G10">
         <v>102.3</v>
@@ -2107,45 +2107,45 @@
         <v>336.1000000000001</v>
       </c>
       <c r="M10">
-        <v>34.84663279999999</v>
+        <v>40.37152139999999</v>
       </c>
       <c r="N10">
-        <v>301.2533672000001</v>
+        <v>295.7284786000001</v>
       </c>
       <c r="O10">
-        <v>96.40107750400004</v>
+        <v>94.63311315200005</v>
       </c>
       <c r="P10">
-        <v>204.8522896960001</v>
+        <v>201.0953654480001</v>
       </c>
       <c r="Q10">
-        <v>1584.652289696</v>
+        <v>1580.895365448</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.08909280968362962</v>
+        <v>0.08942481574861713</v>
       </c>
       <c r="T10">
-        <v>0.5642504407268899</v>
+        <v>0.5685775927380942</v>
       </c>
       <c r="U10">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V10">
         <v>0.32</v>
       </c>
       <c r="W10">
-        <v>0.034204</v>
+        <v>0.035224</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y10">
-        <v>9.645121292752284</v>
+        <v>8.325175478772028</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.0845467423312416</v>
+        <v>0.08431017975354391</v>
       </c>
       <c r="C11">
-        <v>7969.921266958636</v>
+        <v>7906.811218142031</v>
       </c>
       <c r="D11">
-        <v>8646.994266958636</v>
+        <v>8670.481218142031</v>
       </c>
       <c r="E11">
-        <v>-768.4270000000001</v>
+        <v>-681.8300000000002</v>
       </c>
       <c r="F11">
-        <v>779.3729999999998</v>
+        <v>865.9699999999998</v>
       </c>
       <c r="G11">
         <v>102.3</v>
@@ -2189,28 +2189,28 @@
         <v>336.1000000000001</v>
       </c>
       <c r="M11">
-        <v>40.37152139999999</v>
+        <v>44.85724599999999</v>
       </c>
       <c r="N11">
-        <v>295.7284786000001</v>
+        <v>291.2427540000002</v>
       </c>
       <c r="O11">
-        <v>94.63311315200005</v>
+        <v>93.19768128000005</v>
       </c>
       <c r="P11">
-        <v>201.0953654480001</v>
+        <v>198.0450727200001</v>
       </c>
       <c r="Q11">
-        <v>1580.895365448</v>
+        <v>1577.84507272</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.08942481574861713</v>
+        <v>0.0897641997261599</v>
       </c>
       <c r="T11">
-        <v>0.5685775927380942</v>
+        <v>0.5730009036828807</v>
       </c>
       <c r="U11">
         <v>0.0518</v>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>8.325175478772028</v>
+        <v>7.492657930894826</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.08431017975354391</v>
+        <v>0.08407361717584624</v>
       </c>
       <c r="C12">
-        <v>7906.81121814203</v>
+        <v>7843.829107264287</v>
       </c>
       <c r="D12">
-        <v>8670.481218142031</v>
+        <v>8694.096107264288</v>
       </c>
       <c r="E12">
-        <v>-681.83</v>
+        <v>-595.2330000000001</v>
       </c>
       <c r="F12">
-        <v>865.9699999999999</v>
+        <v>952.5669999999999</v>
       </c>
       <c r="G12">
         <v>102.3</v>
@@ -2271,28 +2271,28 @@
         <v>336.1000000000001</v>
       </c>
       <c r="M12">
-        <v>44.857246</v>
+        <v>49.34297059999999</v>
       </c>
       <c r="N12">
-        <v>291.2427540000002</v>
+        <v>286.7570294000001</v>
       </c>
       <c r="O12">
-        <v>93.19768128000005</v>
+        <v>91.76224940800005</v>
       </c>
       <c r="P12">
-        <v>198.0450727200001</v>
+        <v>194.9947799920001</v>
       </c>
       <c r="Q12">
-        <v>1577.84507272</v>
+        <v>1574.794779992</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.0897641997261599</v>
+        <v>0.0901112103099396</v>
       </c>
       <c r="T12">
-        <v>0.5730009036828807</v>
+        <v>0.5775236148736175</v>
       </c>
       <c r="U12">
         <v>0.0518</v>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>7.492657930894826</v>
+        <v>6.811507209904386</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.08407361717584624</v>
+        <v>0.08397577459814858</v>
       </c>
       <c r="C13">
-        <v>7843.829107264287</v>
+        <v>7767.036901607152</v>
       </c>
       <c r="D13">
-        <v>8694.096107264288</v>
+        <v>8703.900901607152</v>
       </c>
       <c r="E13">
-        <v>-595.2330000000001</v>
+        <v>-508.6360000000002</v>
       </c>
       <c r="F13">
-        <v>952.5669999999999</v>
+        <v>1039.164</v>
       </c>
       <c r="G13">
         <v>102.3</v>
@@ -2353,45 +2353,45 @@
         <v>336.1000000000001</v>
       </c>
       <c r="M13">
-        <v>49.34297059999999</v>
+        <v>55.59527399999999</v>
       </c>
       <c r="N13">
-        <v>286.7570294000001</v>
+        <v>280.5047260000001</v>
       </c>
       <c r="O13">
-        <v>91.76224940800005</v>
+        <v>89.76151232000004</v>
       </c>
       <c r="P13">
-        <v>194.9947799920001</v>
+        <v>190.7432136800001</v>
       </c>
       <c r="Q13">
-        <v>1574.794779992</v>
+        <v>1570.54321368</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.0901112103099396</v>
+        <v>0.09046610749789612</v>
       </c>
       <c r="T13">
-        <v>0.5775236148736175</v>
+        <v>0.5821491149550529</v>
       </c>
       <c r="U13">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V13">
         <v>0.32</v>
       </c>
       <c r="W13">
-        <v>0.035224</v>
+        <v>0.03638</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y13">
-        <v>6.811507209904386</v>
+        <v>6.045477894398005</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.08397577459814858</v>
+        <v>0.08382149202045092</v>
       </c>
       <c r="C14">
-        <v>7767.036901607152</v>
+        <v>7695.945551727757</v>
       </c>
       <c r="D14">
-        <v>8703.900901607152</v>
+        <v>8719.406551727758</v>
       </c>
       <c r="E14">
-        <v>-508.6360000000002</v>
+        <v>-422.039</v>
       </c>
       <c r="F14">
-        <v>1039.164</v>
+        <v>1125.761</v>
       </c>
       <c r="G14">
         <v>102.3</v>
@@ -2435,45 +2435,45 @@
         <v>336.1000000000001</v>
       </c>
       <c r="M14">
-        <v>55.59527399999999</v>
+        <v>61.1288223</v>
       </c>
       <c r="N14">
-        <v>280.5047260000001</v>
+        <v>274.9711777000001</v>
       </c>
       <c r="O14">
-        <v>89.76151232000004</v>
+        <v>87.99077686400004</v>
       </c>
       <c r="P14">
-        <v>190.7432136800001</v>
+        <v>186.9804008360001</v>
       </c>
       <c r="Q14">
-        <v>1570.54321368</v>
+        <v>1566.780400836</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.09046610749789612</v>
+        <v>0.0908291632418976</v>
       </c>
       <c r="T14">
-        <v>0.5821491149550529</v>
+        <v>0.5868809483716937</v>
       </c>
       <c r="U14">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V14">
         <v>0.32</v>
       </c>
       <c r="W14">
-        <v>0.03638</v>
+        <v>0.036924</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y14">
-        <v>6.045477894398005</v>
+        <v>5.498224689337752</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.08382149202045092</v>
+        <v>0.08360192944275324</v>
       </c>
       <c r="C15">
-        <v>7695.945551727757</v>
+        <v>7631.51044398563</v>
       </c>
       <c r="D15">
-        <v>8719.406551727758</v>
+        <v>8741.56844398563</v>
       </c>
       <c r="E15">
-        <v>-422.039</v>
+        <v>-335.442</v>
       </c>
       <c r="F15">
-        <v>1125.761</v>
+        <v>1212.358</v>
       </c>
       <c r="G15">
         <v>102.3</v>
@@ -2517,28 +2517,28 @@
         <v>336.1000000000001</v>
       </c>
       <c r="M15">
-        <v>61.1288223</v>
+        <v>65.83103939999999</v>
       </c>
       <c r="N15">
-        <v>274.9711777000001</v>
+        <v>270.2689606000001</v>
       </c>
       <c r="O15">
-        <v>87.99077686400004</v>
+        <v>86.48606739200004</v>
       </c>
       <c r="P15">
-        <v>186.9804008360001</v>
+        <v>183.7828932080001</v>
       </c>
       <c r="Q15">
-        <v>1566.780400836</v>
+        <v>1563.582893208</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.0908291632418976</v>
+        <v>0.09120066214273634</v>
       </c>
       <c r="T15">
-        <v>0.5868809483716937</v>
+        <v>0.5917228244259307</v>
       </c>
       <c r="U15">
         <v>0.0543</v>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>5.498224689337752</v>
+        <v>5.105494354385056</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.08360192944275324</v>
+        <v>0.0833823668650556</v>
       </c>
       <c r="C16">
-        <v>7631.51044398563</v>
+        <v>7567.188279937205</v>
       </c>
       <c r="D16">
-        <v>8741.56844398563</v>
+        <v>8763.843279937206</v>
       </c>
       <c r="E16">
-        <v>-335.442</v>
+        <v>-248.845</v>
       </c>
       <c r="F16">
-        <v>1212.358</v>
+        <v>1298.955</v>
       </c>
       <c r="G16">
         <v>102.3</v>
@@ -2599,28 +2599,28 @@
         <v>336.1000000000001</v>
       </c>
       <c r="M16">
-        <v>65.83103939999999</v>
+        <v>70.53325649999999</v>
       </c>
       <c r="N16">
-        <v>270.2689606000001</v>
+        <v>265.5667435000001</v>
       </c>
       <c r="O16">
-        <v>86.48606739200004</v>
+        <v>84.98135792000005</v>
       </c>
       <c r="P16">
-        <v>183.7828932080001</v>
+        <v>180.5853855800001</v>
       </c>
       <c r="Q16">
-        <v>1563.582893208</v>
+        <v>1560.38538558</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.09120066214273634</v>
+        <v>0.09158090219418305</v>
       </c>
       <c r="T16">
-        <v>0.5917228244259307</v>
+        <v>0.5966786269755617</v>
       </c>
       <c r="U16">
         <v>0.0543</v>
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>5.105494354385056</v>
+        <v>4.765128064092718</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.0833823668650556</v>
+        <v>0.08316280428735791</v>
       </c>
       <c r="C17">
-        <v>7567.188279937205</v>
+        <v>7502.979925180907</v>
       </c>
       <c r="D17">
-        <v>8763.843279937206</v>
+        <v>8786.231925180908</v>
       </c>
       <c r="E17">
-        <v>-248.8450000000003</v>
+        <v>-162.248</v>
       </c>
       <c r="F17">
-        <v>1298.955</v>
+        <v>1385.552</v>
       </c>
       <c r="G17">
         <v>102.3</v>
@@ -2681,28 +2681,28 @@
         <v>336.1000000000001</v>
       </c>
       <c r="M17">
-        <v>70.53325649999998</v>
+        <v>75.23547359999999</v>
       </c>
       <c r="N17">
-        <v>265.5667435000001</v>
+        <v>260.8645264000002</v>
       </c>
       <c r="O17">
-        <v>84.98135792000005</v>
+        <v>83.47664844800005</v>
       </c>
       <c r="P17">
-        <v>180.5853855800001</v>
+        <v>177.3878779520001</v>
       </c>
       <c r="Q17">
-        <v>1560.38538558</v>
+        <v>1557.187877952</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.09158090219418305</v>
+        <v>0.091970195580188</v>
       </c>
       <c r="T17">
-        <v>0.5966786269755617</v>
+        <v>0.6017524248239934</v>
       </c>
       <c r="U17">
         <v>0.0543</v>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>4.765128064092719</v>
+        <v>4.467307560086924</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.08316280428735791</v>
+        <v>0.08305884170966026</v>
       </c>
       <c r="C18">
-        <v>7502.979925180907</v>
+        <v>7427.023871350926</v>
       </c>
       <c r="D18">
-        <v>8786.231925180908</v>
+        <v>8796.872871350926</v>
       </c>
       <c r="E18">
-        <v>-162.248</v>
+        <v>-75.65100000000007</v>
       </c>
       <c r="F18">
-        <v>1385.552</v>
+        <v>1472.149</v>
       </c>
       <c r="G18">
         <v>102.3</v>
@@ -2763,45 +2763,45 @@
         <v>336.1000000000001</v>
       </c>
       <c r="M18">
-        <v>75.23547359999999</v>
+        <v>81.40983969999999</v>
       </c>
       <c r="N18">
-        <v>260.8645264000002</v>
+        <v>254.6901603000001</v>
       </c>
       <c r="O18">
-        <v>83.47664844800005</v>
+        <v>81.50085129600005</v>
       </c>
       <c r="P18">
-        <v>177.3878779520001</v>
+        <v>173.1893090040001</v>
       </c>
       <c r="Q18">
-        <v>1557.187877952</v>
+        <v>1552.989309004</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.091970195580188</v>
+        <v>0.09236886952971116</v>
       </c>
       <c r="T18">
-        <v>0.6017524248239934</v>
+        <v>0.6069484828615439</v>
       </c>
       <c r="U18">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V18">
         <v>0.32</v>
       </c>
       <c r="W18">
-        <v>0.036924</v>
+        <v>0.037604</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y18">
-        <v>4.467307560086924</v>
+        <v>4.128493573240633</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.08305884170966026</v>
+        <v>0.08284607913196258</v>
       </c>
       <c r="C19">
-        <v>7427.023871350926</v>
+        <v>7362.284440217626</v>
       </c>
       <c r="D19">
-        <v>8796.872871350926</v>
+        <v>8818.730440217627</v>
       </c>
       <c r="E19">
-        <v>-75.65100000000007</v>
+        <v>10.94600000000014</v>
       </c>
       <c r="F19">
-        <v>1472.149</v>
+        <v>1558.746</v>
       </c>
       <c r="G19">
         <v>102.3</v>
@@ -2845,28 +2845,28 @@
         <v>336.1000000000001</v>
       </c>
       <c r="M19">
-        <v>81.40983969999999</v>
+        <v>86.1986538</v>
       </c>
       <c r="N19">
-        <v>254.6901603000001</v>
+        <v>249.9013462000001</v>
       </c>
       <c r="O19">
-        <v>81.50085129600005</v>
+        <v>79.96843078400005</v>
       </c>
       <c r="P19">
-        <v>173.1893090040001</v>
+        <v>169.9329154160001</v>
       </c>
       <c r="Q19">
-        <v>1552.989309004</v>
+        <v>1549.732915416</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.09236886952971116</v>
+        <v>0.09277726723410071</v>
       </c>
       <c r="T19">
-        <v>0.6069484828615439</v>
+        <v>0.6122712740219614</v>
       </c>
       <c r="U19">
         <v>0.0553</v>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>4.128493573240633</v>
+        <v>3.899132819171709</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.0828460791319626</v>
+        <v>0.08263331655426492</v>
       </c>
       <c r="C20">
-        <v>7362.284440217627</v>
+        <v>7297.653898539283</v>
       </c>
       <c r="D20">
-        <v>8818.730440217627</v>
+        <v>8840.696898539283</v>
       </c>
       <c r="E20">
-        <v>10.94599999999969</v>
+        <v>97.54299999999989</v>
       </c>
       <c r="F20">
-        <v>1558.746</v>
+        <v>1645.343</v>
       </c>
       <c r="G20">
         <v>102.3</v>
@@ -2927,28 +2927,28 @@
         <v>336.1000000000001</v>
       </c>
       <c r="M20">
-        <v>86.19865379999999</v>
+        <v>90.9874679</v>
       </c>
       <c r="N20">
-        <v>249.9013462000001</v>
+        <v>245.1125321000001</v>
       </c>
       <c r="O20">
-        <v>79.96843078400005</v>
+        <v>78.43601027200005</v>
       </c>
       <c r="P20">
-        <v>169.9329154160001</v>
+        <v>166.6765218280001</v>
       </c>
       <c r="Q20">
-        <v>1549.732915416</v>
+        <v>1546.476521828</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.09277726723410071</v>
+        <v>0.09319574883242582</v>
       </c>
       <c r="T20">
-        <v>0.6122712740219614</v>
+        <v>0.6177254921246115</v>
       </c>
       <c r="U20">
         <v>0.0553</v>
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>3.899132819171709</v>
+        <v>3.693915302373198</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.08263331655426492</v>
+        <v>0.08242055397656725</v>
       </c>
       <c r="C21">
-        <v>7297.653898539283</v>
+        <v>7233.133062041662</v>
       </c>
       <c r="D21">
-        <v>8840.696898539283</v>
+        <v>8862.773062041662</v>
       </c>
       <c r="E21">
-        <v>97.54299999999989</v>
+        <v>184.1399999999999</v>
       </c>
       <c r="F21">
-        <v>1645.343</v>
+        <v>1731.94</v>
       </c>
       <c r="G21">
         <v>102.3</v>
@@ -3009,28 +3009,28 @@
         <v>336.1000000000001</v>
       </c>
       <c r="M21">
-        <v>90.9874679</v>
+        <v>95.77628199999999</v>
       </c>
       <c r="N21">
-        <v>245.1125321000001</v>
+        <v>240.3237180000002</v>
       </c>
       <c r="O21">
-        <v>78.43601027200005</v>
+        <v>76.90358976000005</v>
       </c>
       <c r="P21">
-        <v>166.6765218280001</v>
+        <v>163.4201282400001</v>
       </c>
       <c r="Q21">
-        <v>1546.476521828</v>
+        <v>1543.22012824</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.09319574883242582</v>
+        <v>0.09362469247070906</v>
       </c>
       <c r="T21">
-        <v>0.6177254921246115</v>
+        <v>0.6233160656798278</v>
       </c>
       <c r="U21">
         <v>0.0553</v>
@@ -3047,7 +3047,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>3.693915302373198</v>
+        <v>3.509219537254539</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.08242055397656725</v>
+        <v>0.08220779139886959</v>
       </c>
       <c r="C22">
-        <v>7233.133062041662</v>
+        <v>7168.722754618735</v>
       </c>
       <c r="D22">
-        <v>8862.773062041662</v>
+        <v>8884.959754618736</v>
       </c>
       <c r="E22">
-        <v>184.1399999999999</v>
+        <v>270.7370000000001</v>
       </c>
       <c r="F22">
-        <v>1731.94</v>
+        <v>1818.537</v>
       </c>
       <c r="G22">
         <v>102.3</v>
@@ -3091,28 +3091,28 @@
         <v>336.1000000000001</v>
       </c>
       <c r="M22">
-        <v>95.77628199999999</v>
+        <v>100.5650961</v>
       </c>
       <c r="N22">
-        <v>240.3237180000002</v>
+        <v>235.5349039000001</v>
       </c>
       <c r="O22">
-        <v>76.90358976000005</v>
+        <v>75.37116924800004</v>
       </c>
       <c r="P22">
-        <v>163.4201282400001</v>
+        <v>160.1637346520001</v>
       </c>
       <c r="Q22">
-        <v>1543.22012824</v>
+        <v>1539.963734652</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.09362469247070906</v>
+        <v>0.09406449544160707</v>
       </c>
       <c r="T22">
-        <v>0.6233160656798278</v>
+        <v>0.6290481727427711</v>
       </c>
       <c r="U22">
         <v>0.0553</v>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>3.509219537254539</v>
+        <v>3.342113845004322</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.08220779139886959</v>
+        <v>0.08199502882117192</v>
       </c>
       <c r="C23">
-        <v>7168.722754618735</v>
+        <v>7104.423808435202</v>
       </c>
       <c r="D23">
-        <v>8884.959754618736</v>
+        <v>8907.257808435203</v>
       </c>
       <c r="E23">
-        <v>270.7369999999999</v>
+        <v>357.3339999999998</v>
       </c>
       <c r="F23">
-        <v>1818.537</v>
+        <v>1905.134</v>
       </c>
       <c r="G23">
         <v>102.3</v>
@@ -3173,28 +3173,28 @@
         <v>336.1000000000001</v>
       </c>
       <c r="M23">
-        <v>100.5650961</v>
+        <v>105.3539102</v>
       </c>
       <c r="N23">
-        <v>235.5349039000001</v>
+        <v>230.7460898000002</v>
       </c>
       <c r="O23">
-        <v>75.37116924800004</v>
+        <v>73.83874873600006</v>
       </c>
       <c r="P23">
-        <v>160.1637346520001</v>
+        <v>156.9073410640001</v>
       </c>
       <c r="Q23">
-        <v>1539.963734652</v>
+        <v>1536.707341064</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.09406449544160707</v>
+        <v>0.09451557541175887</v>
       </c>
       <c r="T23">
-        <v>0.6290481727427711</v>
+        <v>0.6349272569098926</v>
       </c>
       <c r="U23">
         <v>0.0553</v>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>3.342113845004322</v>
+        <v>3.190199579322308</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.08199502882117192</v>
+        <v>0.08178226624347426</v>
       </c>
       <c r="C24">
-        <v>7104.423808435202</v>
+        <v>7040.237064030496</v>
       </c>
       <c r="D24">
-        <v>8907.257808435203</v>
+        <v>8929.668064030497</v>
       </c>
       <c r="E24">
-        <v>357.3339999999998</v>
+        <v>443.9309999999998</v>
       </c>
       <c r="F24">
-        <v>1905.134</v>
+        <v>1991.731</v>
       </c>
       <c r="G24">
         <v>102.3</v>
@@ -3255,28 +3255,28 @@
         <v>336.1000000000001</v>
       </c>
       <c r="M24">
-        <v>105.3539102</v>
+        <v>110.1427243</v>
       </c>
       <c r="N24">
-        <v>230.7460898000002</v>
+        <v>225.9572757000001</v>
       </c>
       <c r="O24">
-        <v>73.83874873600006</v>
+        <v>72.30632822400004</v>
       </c>
       <c r="P24">
-        <v>156.9073410640001</v>
+        <v>153.6509474760001</v>
       </c>
       <c r="Q24">
-        <v>1536.707341064</v>
+        <v>1533.450947476</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.09451557541175887</v>
+        <v>0.09497837174477176</v>
       </c>
       <c r="T24">
-        <v>0.6349272569098926</v>
+        <v>0.6409590445618742</v>
       </c>
       <c r="U24">
         <v>0.0553</v>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>3.190199579322308</v>
+        <v>3.051495249786555</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.08178226624347426</v>
+        <v>0.08197750366577659</v>
       </c>
       <c r="C25">
-        <v>7040.237064030496</v>
+        <v>6933.071478957461</v>
       </c>
       <c r="D25">
-        <v>8929.668064030497</v>
+        <v>8909.099478957462</v>
       </c>
       <c r="E25">
-        <v>443.9309999999998</v>
+        <v>530.528</v>
       </c>
       <c r="F25">
-        <v>1991.731</v>
+        <v>2078.328</v>
       </c>
       <c r="G25">
         <v>102.3</v>
@@ -3337,45 +3337,45 @@
         <v>336.1000000000001</v>
       </c>
       <c r="M25">
-        <v>110.1427243</v>
+        <v>120.1273584</v>
       </c>
       <c r="N25">
-        <v>225.9572757000001</v>
+        <v>215.9726416000001</v>
       </c>
       <c r="O25">
-        <v>72.30632822400004</v>
+        <v>69.11124531200005</v>
       </c>
       <c r="P25">
-        <v>153.6509474760001</v>
+        <v>146.8613962880001</v>
       </c>
       <c r="Q25">
-        <v>1533.450947476</v>
+        <v>1526.661396288</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.09497837174477176</v>
+        <v>0.09545334692865341</v>
       </c>
       <c r="T25">
-        <v>0.6409590445618742</v>
+        <v>0.6471495634678555</v>
       </c>
       <c r="U25">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V25">
         <v>0.32</v>
       </c>
       <c r="W25">
-        <v>0.037604</v>
+        <v>0.039304</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y25">
-        <v>3.051495249786555</v>
+        <v>2.797863904414301</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.08197750366577659</v>
+        <v>0.08178174108807892</v>
       </c>
       <c r="C26">
-        <v>6933.071478957461</v>
+        <v>6867.098518095621</v>
       </c>
       <c r="D26">
-        <v>8909.099478957462</v>
+        <v>8929.723518095621</v>
       </c>
       <c r="E26">
-        <v>530.5279999999996</v>
+        <v>617.1249999999998</v>
       </c>
       <c r="F26">
-        <v>2078.328</v>
+        <v>2164.925</v>
       </c>
       <c r="G26">
         <v>102.3</v>
@@ -3419,28 +3419,28 @@
         <v>336.1000000000001</v>
       </c>
       <c r="M26">
-        <v>120.1273584</v>
+        <v>125.132665</v>
       </c>
       <c r="N26">
-        <v>215.9726416000001</v>
+        <v>210.9673350000002</v>
       </c>
       <c r="O26">
-        <v>69.11124531200005</v>
+        <v>67.50954720000006</v>
       </c>
       <c r="P26">
-        <v>146.8613962880001</v>
+        <v>143.4577878000001</v>
       </c>
       <c r="Q26">
-        <v>1526.661396288</v>
+        <v>1523.2577878</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.09545334692865341</v>
+        <v>0.09594098811743856</v>
       </c>
       <c r="T26">
-        <v>0.6471495634678555</v>
+        <v>0.6535051628779961</v>
       </c>
       <c r="U26">
         <v>0.0578</v>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>2.797863904414302</v>
+        <v>2.68594934823773</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.08178174108807892</v>
+        <v>0.08158597851038125</v>
       </c>
       <c r="C27">
-        <v>6867.098518095621</v>
+        <v>6801.221265658302</v>
       </c>
       <c r="D27">
-        <v>8929.723518095621</v>
+        <v>8950.443265658303</v>
       </c>
       <c r="E27">
-        <v>617.1249999999998</v>
+        <v>703.722</v>
       </c>
       <c r="F27">
-        <v>2164.925</v>
+        <v>2251.522</v>
       </c>
       <c r="G27">
         <v>102.3</v>
@@ -3501,28 +3501,28 @@
         <v>336.1000000000001</v>
       </c>
       <c r="M27">
-        <v>125.132665</v>
+        <v>130.1379716</v>
       </c>
       <c r="N27">
-        <v>210.9673350000002</v>
+        <v>205.9620284000001</v>
       </c>
       <c r="O27">
-        <v>67.50954720000006</v>
+        <v>65.90784908800003</v>
       </c>
       <c r="P27">
-        <v>143.4577878000001</v>
+        <v>140.0541793120001</v>
       </c>
       <c r="Q27">
-        <v>1523.2577878</v>
+        <v>1519.854179312</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.09594098811743856</v>
+        <v>0.09644180879781251</v>
       </c>
       <c r="T27">
-        <v>0.6535051628779961</v>
+        <v>0.6600325352451677</v>
       </c>
       <c r="U27">
         <v>0.0578</v>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>2.68594934823773</v>
+        <v>2.58264360407474</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.08158597851038125</v>
+        <v>0.08203281593268359</v>
       </c>
       <c r="C28">
-        <v>6801.221265658302</v>
+        <v>6667.470454139174</v>
       </c>
       <c r="D28">
-        <v>8950.443265658303</v>
+        <v>8903.289454139174</v>
       </c>
       <c r="E28">
-        <v>703.722</v>
+        <v>790.3189999999997</v>
       </c>
       <c r="F28">
-        <v>2251.522</v>
+        <v>2338.119</v>
       </c>
       <c r="G28">
         <v>102.3</v>
@@ -3583,45 +3583,45 @@
         <v>336.1000000000001</v>
       </c>
       <c r="M28">
-        <v>130.1379716</v>
+        <v>143.3266947</v>
       </c>
       <c r="N28">
-        <v>205.9620284000001</v>
+        <v>192.7733053000001</v>
       </c>
       <c r="O28">
-        <v>65.90784908800003</v>
+        <v>61.68745769600005</v>
       </c>
       <c r="P28">
-        <v>140.0541793120001</v>
+        <v>131.0858476040001</v>
       </c>
       <c r="Q28">
-        <v>1519.854179312</v>
+        <v>1510.885847604</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.09644180879781251</v>
+        <v>0.09695635059271725</v>
       </c>
       <c r="T28">
-        <v>0.6600325352451677</v>
+        <v>0.6667387397319877</v>
       </c>
       <c r="U28">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V28">
         <v>0.32</v>
       </c>
       <c r="W28">
-        <v>0.039304</v>
+        <v>0.041684</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y28">
-        <v>2.58264360407474</v>
+        <v>2.344992331704138</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.08203281593268359</v>
+        <v>0.08186085335498593</v>
       </c>
       <c r="C29">
-        <v>6667.470454139174</v>
+        <v>6598.961372042966</v>
       </c>
       <c r="D29">
-        <v>8903.289454139174</v>
+        <v>8921.377372042967</v>
       </c>
       <c r="E29">
-        <v>790.3189999999997</v>
+        <v>876.9159999999999</v>
       </c>
       <c r="F29">
-        <v>2338.119</v>
+        <v>2424.716</v>
       </c>
       <c r="G29">
         <v>102.3</v>
@@ -3665,28 +3665,28 @@
         <v>336.1000000000001</v>
       </c>
       <c r="M29">
-        <v>143.3266947</v>
+        <v>148.6350908</v>
       </c>
       <c r="N29">
-        <v>192.7733053000001</v>
+        <v>187.4649092000001</v>
       </c>
       <c r="O29">
-        <v>61.68745769600005</v>
+        <v>59.98877094400004</v>
       </c>
       <c r="P29">
-        <v>131.0858476040001</v>
+        <v>127.4761382560001</v>
       </c>
       <c r="Q29">
-        <v>1510.885847604</v>
+        <v>1507.276138256</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.09695635059271725</v>
+        <v>0.09748518521525823</v>
       </c>
       <c r="T29">
-        <v>0.6667387397319877</v>
+        <v>0.6736312276767751</v>
       </c>
       <c r="U29">
         <v>0.0613</v>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>2.344992331704138</v>
+        <v>2.261242605571848</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.08186085335498593</v>
+        <v>0.08224105077728826</v>
       </c>
       <c r="C30">
-        <v>6598.961372042966</v>
+        <v>6472.471173988792</v>
       </c>
       <c r="D30">
-        <v>8921.377372042967</v>
+        <v>8881.484173988792</v>
       </c>
       <c r="E30">
-        <v>876.9159999999999</v>
+        <v>963.5130000000001</v>
       </c>
       <c r="F30">
-        <v>2424.716</v>
+        <v>2511.313</v>
       </c>
       <c r="G30">
         <v>102.3</v>
@@ -3747,45 +3747,45 @@
         <v>336.1000000000001</v>
       </c>
       <c r="M30">
-        <v>148.6350908</v>
+        <v>160.9751633</v>
       </c>
       <c r="N30">
-        <v>187.4649092000001</v>
+        <v>175.1248367000001</v>
       </c>
       <c r="O30">
-        <v>59.98877094400004</v>
+        <v>56.03994774400004</v>
       </c>
       <c r="P30">
-        <v>127.4761382560001</v>
+        <v>119.0848889560001</v>
       </c>
       <c r="Q30">
-        <v>1507.276138256</v>
+        <v>1498.884888956</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.09748518521525823</v>
+        <v>0.09802891658772994</v>
       </c>
       <c r="T30">
-        <v>0.6736312276767751</v>
+        <v>0.6807178702115563</v>
       </c>
       <c r="U30">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V30">
         <v>0.32</v>
       </c>
       <c r="W30">
-        <v>0.041684</v>
+        <v>0.043588</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y30">
-        <v>2.261242605571848</v>
+        <v>2.087899730057302</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.08224105077728826</v>
+        <v>0.08208812819959059</v>
       </c>
       <c r="C31">
-        <v>6472.471173988792</v>
+        <v>6401.877002339634</v>
       </c>
       <c r="D31">
-        <v>8881.484173988792</v>
+        <v>8897.487002339634</v>
       </c>
       <c r="E31">
-        <v>963.5129999999997</v>
+        <v>1050.109999999999</v>
       </c>
       <c r="F31">
-        <v>2511.313</v>
+        <v>2597.909999999999</v>
       </c>
       <c r="G31">
         <v>102.3</v>
@@ -3829,28 +3829,28 @@
         <v>336.1000000000001</v>
       </c>
       <c r="M31">
-        <v>160.9751633</v>
+        <v>166.526031</v>
       </c>
       <c r="N31">
-        <v>175.1248367000001</v>
+        <v>169.5739690000002</v>
       </c>
       <c r="O31">
-        <v>56.03994774400005</v>
+        <v>54.26367008000005</v>
       </c>
       <c r="P31">
-        <v>119.0848889560001</v>
+        <v>115.3102989200001</v>
       </c>
       <c r="Q31">
-        <v>1498.884888956</v>
+        <v>1495.11029892</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.09802891658772994</v>
+        <v>0.09858818314227227</v>
       </c>
       <c r="T31">
-        <v>0.6807178702115563</v>
+        <v>0.6880069882473313</v>
       </c>
       <c r="U31">
         <v>0.0641</v>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>2.087899730057302</v>
+        <v>2.018303072388726</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.08208812819959059</v>
+        <v>0.08440156562189292</v>
       </c>
       <c r="C32">
-        <v>6401.877002339634</v>
+        <v>6079.18592735657</v>
       </c>
       <c r="D32">
-        <v>8897.487002339634</v>
+        <v>8661.39292735657</v>
       </c>
       <c r="E32">
-        <v>1050.109999999999</v>
+        <v>1136.707</v>
       </c>
       <c r="F32">
-        <v>2597.909999999999</v>
+        <v>2684.507</v>
       </c>
       <c r="G32">
         <v>102.3</v>
@@ -3911,45 +3911,45 @@
         <v>336.1000000000001</v>
       </c>
       <c r="M32">
-        <v>166.526031</v>
+        <v>203.4856306</v>
       </c>
       <c r="N32">
-        <v>169.5739690000002</v>
+        <v>132.6143694000002</v>
       </c>
       <c r="O32">
-        <v>54.26367008000005</v>
+        <v>42.43659820800005</v>
       </c>
       <c r="P32">
-        <v>115.3102989200001</v>
+        <v>90.17777119200011</v>
       </c>
       <c r="Q32">
-        <v>1495.11029892</v>
+        <v>1469.977771192</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.09858818314227227</v>
+        <v>0.09916366032158395</v>
       </c>
       <c r="T32">
-        <v>0.6880069882473313</v>
+        <v>0.695507385066752</v>
       </c>
       <c r="U32">
-        <v>0.0641</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V32">
         <v>0.32</v>
       </c>
       <c r="W32">
-        <v>0.043588</v>
+        <v>0.051544</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y32">
-        <v>2.018303072388726</v>
+        <v>1.651713681250966</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.08440156562189292</v>
+        <v>0.08432820304419528</v>
       </c>
       <c r="C33">
-        <v>6079.18592735657</v>
+        <v>5999.883299042252</v>
       </c>
       <c r="D33">
-        <v>8661.39292735657</v>
+        <v>8668.687299042253</v>
       </c>
       <c r="E33">
-        <v>1136.707</v>
+        <v>1223.304</v>
       </c>
       <c r="F33">
-        <v>2684.507</v>
+        <v>2771.104</v>
       </c>
       <c r="G33">
         <v>102.3</v>
@@ -3993,28 +3993,28 @@
         <v>336.1000000000001</v>
       </c>
       <c r="M33">
-        <v>203.4856306</v>
+        <v>210.0496832</v>
       </c>
       <c r="N33">
-        <v>132.6143694000002</v>
+        <v>126.0503168000001</v>
       </c>
       <c r="O33">
-        <v>42.43659820800005</v>
+        <v>40.33610137600004</v>
       </c>
       <c r="P33">
-        <v>90.17777119200011</v>
+        <v>85.71421542400009</v>
       </c>
       <c r="Q33">
-        <v>1469.977771192</v>
+        <v>1465.514215424</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.09916366032158395</v>
+        <v>0.09975606330028716</v>
       </c>
       <c r="T33">
-        <v>0.695507385066752</v>
+        <v>0.7032283817926264</v>
       </c>
       <c r="U33">
         <v>0.07580000000000001</v>
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>1.651713681250966</v>
+        <v>1.600097628711873</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.08432820304419528</v>
+        <v>0.0842548404664976</v>
       </c>
       <c r="C34">
-        <v>5999.883299042252</v>
+        <v>5920.592967296541</v>
       </c>
       <c r="D34">
-        <v>8668.687299042253</v>
+        <v>8675.993967296541</v>
       </c>
       <c r="E34">
-        <v>1223.304</v>
+        <v>1309.901</v>
       </c>
       <c r="F34">
-        <v>2771.104</v>
+        <v>2857.701</v>
       </c>
       <c r="G34">
         <v>102.3</v>
@@ -4075,28 +4075,28 @@
         <v>336.1000000000001</v>
       </c>
       <c r="M34">
-        <v>210.0496832</v>
+        <v>216.6137358</v>
       </c>
       <c r="N34">
-        <v>126.0503168000001</v>
+        <v>119.4862642000002</v>
       </c>
       <c r="O34">
-        <v>40.33610137600004</v>
+        <v>38.23560454400005</v>
       </c>
       <c r="P34">
-        <v>85.71421542400009</v>
+        <v>81.25065965600011</v>
       </c>
       <c r="Q34">
-        <v>1465.514215424</v>
+        <v>1461.050659656</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.09975606330028716</v>
+        <v>0.1003661499499964</v>
       </c>
       <c r="T34">
-        <v>0.7032283817926264</v>
+        <v>0.7111798560327058</v>
       </c>
       <c r="U34">
         <v>0.07580000000000001</v>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>1.600097628711873</v>
+        <v>1.55160982178121</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.0842548404664976</v>
+        <v>0.08418147788879993</v>
       </c>
       <c r="C35">
-        <v>5920.592967296541</v>
+        <v>5841.314963239279</v>
       </c>
       <c r="D35">
-        <v>8675.993967296541</v>
+        <v>8683.312963239279</v>
       </c>
       <c r="E35">
-        <v>1309.901</v>
+        <v>1396.498</v>
       </c>
       <c r="F35">
-        <v>2857.701</v>
+        <v>2944.298</v>
       </c>
       <c r="G35">
         <v>102.3</v>
@@ -4157,28 +4157,28 @@
         <v>336.1000000000001</v>
       </c>
       <c r="M35">
-        <v>216.6137358</v>
+        <v>223.1777884</v>
       </c>
       <c r="N35">
-        <v>119.4862642000002</v>
+        <v>112.9222116000001</v>
       </c>
       <c r="O35">
-        <v>38.23560454400005</v>
+        <v>36.13510771200004</v>
       </c>
       <c r="P35">
-        <v>81.25065965600011</v>
+        <v>76.7871038880001</v>
       </c>
       <c r="Q35">
-        <v>1461.050659656</v>
+        <v>1456.587103888</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1003661499499964</v>
+        <v>0.1009947240739393</v>
       </c>
       <c r="T35">
-        <v>0.7111798560327058</v>
+        <v>0.7193722840376361</v>
       </c>
       <c r="U35">
         <v>0.07580000000000001</v>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>1.55160982178121</v>
+        <v>1.505974238787645</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.08418147788879993</v>
+        <v>0.09545544836598116</v>
       </c>
       <c r="C36">
-        <v>5841.314963239279</v>
+        <v>4758.210678062251</v>
       </c>
       <c r="D36">
-        <v>8683.312963239279</v>
+        <v>7686.805678062251</v>
       </c>
       <c r="E36">
-        <v>1396.498</v>
+        <v>1483.095</v>
       </c>
       <c r="F36">
-        <v>2944.298</v>
+        <v>3030.895</v>
       </c>
       <c r="G36">
         <v>102.3</v>
@@ -4239,45 +4239,45 @@
         <v>336.1000000000001</v>
       </c>
       <c r="M36">
-        <v>223.1777884</v>
+        <v>359.464147</v>
       </c>
       <c r="N36">
-        <v>112.9222116000001</v>
+        <v>-23.36414699999989</v>
       </c>
       <c r="O36">
-        <v>36.13510771200004</v>
+        <v>-7.476527039999965</v>
       </c>
       <c r="P36">
-        <v>76.7871038880001</v>
+        <v>-15.88761995999992</v>
       </c>
       <c r="Q36">
-        <v>1456.587103888</v>
+        <v>1363.91238004</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1009947240739393</v>
+        <v>0.1021004279265114</v>
       </c>
       <c r="T36">
-        <v>0.7193722840376361</v>
+        <v>0.7337833118892926</v>
       </c>
       <c r="U36">
-        <v>0.07580000000000001</v>
+        <v>0.1186</v>
       </c>
       <c r="V36">
-        <v>0.32</v>
+        <v>0.2992009102927309</v>
       </c>
       <c r="W36">
-        <v>0.051544</v>
+        <v>0.08311477203928212</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y36">
-        <v>1.505974238787645</v>
+        <v>0.9350028446647841</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.09545544836598116</v>
+        <v>0.09618344836598117</v>
       </c>
       <c r="C37">
-        <v>4758.210678062251</v>
+        <v>4615.06936601825</v>
       </c>
       <c r="D37">
-        <v>7686.805678062251</v>
+        <v>7630.26136601825</v>
       </c>
       <c r="E37">
-        <v>1483.095</v>
+        <v>1569.692</v>
       </c>
       <c r="F37">
-        <v>3030.895</v>
+        <v>3117.492</v>
       </c>
       <c r="G37">
         <v>102.3</v>
@@ -4321,37 +4321,37 @@
         <v>336.1000000000001</v>
       </c>
       <c r="M37">
-        <v>359.464147</v>
+        <v>369.7345512000001</v>
       </c>
       <c r="N37">
-        <v>-23.36414699999989</v>
+        <v>-33.63455119999992</v>
       </c>
       <c r="O37">
-        <v>-7.476527039999965</v>
+        <v>-10.76305638399997</v>
       </c>
       <c r="P37">
-        <v>-15.88761995999992</v>
+        <v>-22.87149481599995</v>
       </c>
       <c r="Q37">
-        <v>1363.91238004</v>
+        <v>1356.928505184</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1021004279265114</v>
+        <v>0.1029801221128632</v>
       </c>
       <c r="T37">
-        <v>0.7337833118892926</v>
+        <v>0.7452486761375628</v>
       </c>
       <c r="U37">
         <v>0.1186</v>
       </c>
       <c r="V37">
-        <v>0.2992009102927309</v>
+        <v>0.2908897738957106</v>
       </c>
       <c r="W37">
-        <v>0.08311477203928212</v>
+        <v>0.08410047281596873</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>0.9350028446647841</v>
+        <v>0.9090305434240956</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.09618344836598117</v>
+        <v>0.09691144836598117</v>
       </c>
       <c r="C38">
-        <v>4615.069366018251</v>
+        <v>4472.753861726347</v>
       </c>
       <c r="D38">
-        <v>7630.26136601825</v>
+        <v>7574.542861726347</v>
       </c>
       <c r="E38">
-        <v>1569.691999999999</v>
+        <v>1656.289</v>
       </c>
       <c r="F38">
-        <v>3117.491999999999</v>
+        <v>3204.088999999999</v>
       </c>
       <c r="G38">
         <v>102.3</v>
@@ -4403,37 +4403,37 @@
         <v>336.1000000000001</v>
       </c>
       <c r="M38">
-        <v>369.7345511999999</v>
+        <v>380.0049554</v>
       </c>
       <c r="N38">
-        <v>-33.63455119999981</v>
+        <v>-43.90495539999984</v>
       </c>
       <c r="O38">
-        <v>-10.76305638399994</v>
+        <v>-14.04958572799995</v>
       </c>
       <c r="P38">
-        <v>-22.87149481599987</v>
+        <v>-29.85536967199989</v>
       </c>
       <c r="Q38">
-        <v>1356.928505184</v>
+        <v>1349.944630328</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1029801221128632</v>
+        <v>0.1038877430987816</v>
       </c>
       <c r="T38">
-        <v>0.7452486761375628</v>
+        <v>0.7570780202032384</v>
       </c>
       <c r="U38">
         <v>0.1186</v>
       </c>
       <c r="V38">
-        <v>0.2908897738957107</v>
+        <v>0.2830278881147455</v>
       </c>
       <c r="W38">
-        <v>0.08410047281596872</v>
+        <v>0.0850328924695912</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>0.9090305434240958</v>
+        <v>0.8844621503585797</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.09691144836598117</v>
+        <v>0.09763944836598118</v>
       </c>
       <c r="C39">
-        <v>4472.753861726347</v>
+        <v>4331.246205431165</v>
       </c>
       <c r="D39">
-        <v>7574.542861726347</v>
+        <v>7519.632205431164</v>
       </c>
       <c r="E39">
-        <v>1656.289</v>
+        <v>1742.886</v>
       </c>
       <c r="F39">
-        <v>3204.088999999999</v>
+        <v>3290.686</v>
       </c>
       <c r="G39">
         <v>102.3</v>
@@ -4485,37 +4485,37 @@
         <v>336.1000000000001</v>
       </c>
       <c r="M39">
-        <v>380.0049554</v>
+        <v>390.2753596</v>
       </c>
       <c r="N39">
-        <v>-43.90495539999984</v>
+        <v>-54.17535959999987</v>
       </c>
       <c r="O39">
-        <v>-14.04958572799995</v>
+        <v>-17.33611507199996</v>
       </c>
       <c r="P39">
-        <v>-29.85536967199989</v>
+        <v>-36.83924452799991</v>
       </c>
       <c r="Q39">
-        <v>1349.944630328</v>
+        <v>1342.960755472</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1038877430987816</v>
+        <v>0.1048246421810201</v>
       </c>
       <c r="T39">
-        <v>0.7570780202032384</v>
+        <v>0.7692889560129681</v>
       </c>
       <c r="U39">
         <v>0.1186</v>
       </c>
       <c r="V39">
-        <v>0.2830278881147455</v>
+        <v>0.2755797857959364</v>
       </c>
       <c r="W39">
-        <v>0.0850328924695912</v>
+        <v>0.08591623740460196</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>0.8844621503585797</v>
+        <v>0.8611868306123012</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.09763944836598118</v>
+        <v>0.09836744836598119</v>
       </c>
       <c r="C40">
-        <v>4331.246205431165</v>
+        <v>4190.528954416686</v>
       </c>
       <c r="D40">
-        <v>7519.632205431164</v>
+        <v>7465.511954416686</v>
       </c>
       <c r="E40">
-        <v>1742.886</v>
+        <v>1829.483</v>
       </c>
       <c r="F40">
-        <v>3290.686</v>
+        <v>3377.283</v>
       </c>
       <c r="G40">
         <v>102.3</v>
@@ -4567,37 +4567,37 @@
         <v>336.1000000000001</v>
       </c>
       <c r="M40">
-        <v>390.2753596</v>
+        <v>400.5457638</v>
       </c>
       <c r="N40">
-        <v>-54.17535959999987</v>
+        <v>-64.4457637999999</v>
       </c>
       <c r="O40">
-        <v>-17.33611507199996</v>
+        <v>-20.62264441599997</v>
       </c>
       <c r="P40">
-        <v>-36.83924452799991</v>
+        <v>-43.82311938399992</v>
       </c>
       <c r="Q40">
-        <v>1342.960755472</v>
+        <v>1335.976880616</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1048246421810201</v>
+        <v>0.1057922592659548</v>
       </c>
       <c r="T40">
-        <v>0.7692889560129681</v>
+        <v>0.7819002503738364</v>
       </c>
       <c r="U40">
         <v>0.1186</v>
       </c>
       <c r="V40">
-        <v>0.2755797857959364</v>
+        <v>0.2685136374421944</v>
       </c>
       <c r="W40">
-        <v>0.08591623740460196</v>
+        <v>0.08675428259935576</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>0.8611868306123012</v>
+        <v>0.8391051170068575</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.09836744836598119</v>
+        <v>0.09909544836598119</v>
       </c>
       <c r="C41">
-        <v>4190.528954416686</v>
+        <v>4050.585164533059</v>
       </c>
       <c r="D41">
-        <v>7465.511954416686</v>
+        <v>7412.165164533058</v>
       </c>
       <c r="E41">
-        <v>1829.483</v>
+        <v>1916.08</v>
       </c>
       <c r="F41">
-        <v>3377.283</v>
+        <v>3463.88</v>
       </c>
       <c r="G41">
         <v>102.3</v>
@@ -4649,37 +4649,37 @@
         <v>336.1000000000001</v>
       </c>
       <c r="M41">
-        <v>400.5457638</v>
+        <v>410.816168</v>
       </c>
       <c r="N41">
-        <v>-64.4457637999999</v>
+        <v>-74.71616799999987</v>
       </c>
       <c r="O41">
-        <v>-20.62264441599997</v>
+        <v>-23.90917375999996</v>
       </c>
       <c r="P41">
-        <v>-43.82311938399992</v>
+        <v>-50.80699423999991</v>
       </c>
       <c r="Q41">
-        <v>1335.976880616</v>
+        <v>1328.99300576</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1057922592659548</v>
+        <v>0.1067921302537207</v>
       </c>
       <c r="T41">
-        <v>0.7819002503738364</v>
+        <v>0.7949319212134003</v>
       </c>
       <c r="U41">
         <v>0.1186</v>
       </c>
       <c r="V41">
-        <v>0.2685136374421944</v>
+        <v>0.2618007965061396</v>
       </c>
       <c r="W41">
-        <v>0.08675428259935576</v>
+        <v>0.08755042553437187</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>0.8391051170068575</v>
+        <v>0.8181274890816861</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.09909544836598119</v>
+        <v>0.1352777359680493</v>
       </c>
       <c r="C42">
-        <v>4050.585164533059</v>
+        <v>2021.445086546296</v>
       </c>
       <c r="D42">
-        <v>7412.165164533058</v>
+        <v>5469.622086546296</v>
       </c>
       <c r="E42">
-        <v>1916.08</v>
+        <v>2002.677</v>
       </c>
       <c r="F42">
-        <v>3463.88</v>
+        <v>3550.477</v>
       </c>
       <c r="G42">
         <v>102.3</v>
@@ -4731,45 +4731,45 @@
         <v>336.1000000000001</v>
       </c>
       <c r="M42">
-        <v>410.816168</v>
+        <v>712.9357816</v>
       </c>
       <c r="N42">
-        <v>-74.71616799999987</v>
+        <v>-376.8357815999999</v>
       </c>
       <c r="O42">
-        <v>-23.90917375999996</v>
+        <v>-120.587450112</v>
       </c>
       <c r="P42">
-        <v>-50.80699423999991</v>
+        <v>-256.248331488</v>
       </c>
       <c r="Q42">
-        <v>1328.99300576</v>
+        <v>1123.551668512</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1067921302537207</v>
+        <v>0.1107958741598315</v>
       </c>
       <c r="T42">
-        <v>0.7949319212134003</v>
+        <v>0.8471141260665737</v>
       </c>
       <c r="U42">
-        <v>0.1186</v>
+        <v>0.2008</v>
       </c>
       <c r="V42">
-        <v>0.2618007965061396</v>
+        <v>0.1508579072278114</v>
       </c>
       <c r="W42">
-        <v>0.08755042553437187</v>
+        <v>0.1705077322286555</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y42">
-        <v>0.8181274890816861</v>
+        <v>0.4714309600869108</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1352777359680493</v>
+        <v>0.1368277359680493</v>
       </c>
       <c r="C43">
-        <v>2021.445086546296</v>
+        <v>1874.122748874763</v>
       </c>
       <c r="D43">
-        <v>5469.622086546296</v>
+        <v>5408.896748874763</v>
       </c>
       <c r="E43">
-        <v>2002.677</v>
+        <v>2089.274</v>
       </c>
       <c r="F43">
-        <v>3550.477</v>
+        <v>3637.074</v>
       </c>
       <c r="G43">
         <v>102.3</v>
@@ -4813,37 +4813,37 @@
         <v>336.1000000000001</v>
       </c>
       <c r="M43">
-        <v>712.9357816</v>
+        <v>730.3244592000001</v>
       </c>
       <c r="N43">
-        <v>-376.8357815999999</v>
+        <v>-394.2244592</v>
       </c>
       <c r="O43">
-        <v>-120.587450112</v>
+        <v>-126.151826944</v>
       </c>
       <c r="P43">
-        <v>-256.248331488</v>
+        <v>-268.072632256</v>
       </c>
       <c r="Q43">
-        <v>1123.551668512</v>
+        <v>1111.727367744</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1107958741598315</v>
+        <v>0.1119164926798286</v>
       </c>
       <c r="T43">
-        <v>0.8471141260665737</v>
+        <v>0.8617195420332388</v>
       </c>
       <c r="U43">
         <v>0.2008</v>
       </c>
       <c r="V43">
-        <v>0.1508579072278114</v>
+        <v>0.1472660522938159</v>
       </c>
       <c r="W43">
-        <v>0.1705077322286555</v>
+        <v>0.1712289766994018</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>0.4714309600869108</v>
+        <v>0.4602064134181747</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1368277359680493</v>
+        <v>0.1383777359680493</v>
       </c>
       <c r="C44">
-        <v>1874.122748874764</v>
+        <v>1728.133986240189</v>
       </c>
       <c r="D44">
-        <v>5408.896748874763</v>
+        <v>5349.504986240188</v>
       </c>
       <c r="E44">
-        <v>2089.273999999999</v>
+        <v>2175.870999999999</v>
       </c>
       <c r="F44">
-        <v>3637.074</v>
+        <v>3723.670999999999</v>
       </c>
       <c r="G44">
         <v>102.3</v>
@@ -4895,37 +4895,37 @@
         <v>336.1000000000001</v>
       </c>
       <c r="M44">
-        <v>730.3244592</v>
+        <v>747.7131367999999</v>
       </c>
       <c r="N44">
-        <v>-394.2244591999998</v>
+        <v>-411.6131367999998</v>
       </c>
       <c r="O44">
-        <v>-126.151826944</v>
+        <v>-131.7162037759999</v>
       </c>
       <c r="P44">
-        <v>-268.0726322559999</v>
+        <v>-279.8969330239998</v>
       </c>
       <c r="Q44">
-        <v>1111.727367744</v>
+        <v>1099.903066976</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1119164926798286</v>
+        <v>0.1130764311478958</v>
       </c>
       <c r="T44">
-        <v>0.8617195420332385</v>
+        <v>0.876837428735576</v>
       </c>
       <c r="U44">
         <v>0.2008</v>
       </c>
       <c r="V44">
-        <v>0.147266052293816</v>
+        <v>0.1438412603800063</v>
       </c>
       <c r="W44">
-        <v>0.1712289766994018</v>
+        <v>0.1719166749156947</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>0.4602064134181748</v>
+        <v>0.4495039386875196</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1383777359680493</v>
+        <v>0.1399277359680494</v>
       </c>
       <c r="C45">
-        <v>1728.133986240189</v>
+        <v>1583.435346268823</v>
       </c>
       <c r="D45">
-        <v>5349.504986240188</v>
+        <v>5291.403346268822</v>
       </c>
       <c r="E45">
-        <v>2175.870999999999</v>
+        <v>2262.468</v>
       </c>
       <c r="F45">
-        <v>3723.670999999999</v>
+        <v>3810.268</v>
       </c>
       <c r="G45">
         <v>102.3</v>
@@ -4977,37 +4977,37 @@
         <v>336.1000000000001</v>
       </c>
       <c r="M45">
-        <v>747.7131367999999</v>
+        <v>765.1018144</v>
       </c>
       <c r="N45">
-        <v>-411.6131367999998</v>
+        <v>-429.0018143999998</v>
       </c>
       <c r="O45">
-        <v>-131.7162037759999</v>
+        <v>-137.280580608</v>
       </c>
       <c r="P45">
-        <v>-279.8969330239998</v>
+        <v>-291.7212337919999</v>
       </c>
       <c r="Q45">
-        <v>1099.903066976</v>
+        <v>1088.078766208</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1130764311478958</v>
+        <v>0.1142777959898225</v>
       </c>
       <c r="T45">
-        <v>0.876837428735576</v>
+        <v>0.8924952399629973</v>
       </c>
       <c r="U45">
         <v>0.2008</v>
       </c>
       <c r="V45">
-        <v>0.1438412603800063</v>
+        <v>0.1405721408259152</v>
       </c>
       <c r="W45">
-        <v>0.1719166749156947</v>
+        <v>0.1725731141221562</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>0.4495039386875196</v>
+        <v>0.439287940080985</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1399277359680494</v>
+        <v>0.1414777359680493</v>
       </c>
       <c r="C46">
-        <v>1583.435346268823</v>
+        <v>1439.985244070531</v>
       </c>
       <c r="D46">
-        <v>5291.403346268822</v>
+        <v>5234.55024407053</v>
       </c>
       <c r="E46">
-        <v>2262.468</v>
+        <v>2349.065</v>
       </c>
       <c r="F46">
-        <v>3810.268</v>
+        <v>3896.865</v>
       </c>
       <c r="G46">
         <v>102.3</v>
@@ -5059,37 +5059,37 @@
         <v>336.1000000000001</v>
       </c>
       <c r="M46">
-        <v>765.1018144</v>
+        <v>782.490492</v>
       </c>
       <c r="N46">
-        <v>-429.0018143999998</v>
+        <v>-446.3904919999999</v>
       </c>
       <c r="O46">
-        <v>-137.280580608</v>
+        <v>-142.84495744</v>
       </c>
       <c r="P46">
-        <v>-291.7212337919999</v>
+        <v>-303.5455345599999</v>
       </c>
       <c r="Q46">
-        <v>1088.078766208</v>
+        <v>1076.25446544</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1142777959898225</v>
+        <v>0.1155228468260011</v>
       </c>
       <c r="T46">
-        <v>0.8924952399629973</v>
+        <v>0.9087224261441427</v>
       </c>
       <c r="U46">
         <v>0.2008</v>
       </c>
       <c r="V46">
-        <v>0.1405721408259152</v>
+        <v>0.1374483154742282</v>
       </c>
       <c r="W46">
-        <v>0.1725731141221562</v>
+        <v>0.173200378252775</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>0.439287940080985</v>
+        <v>0.4295259858569631</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1414777359680493</v>
+        <v>0.1430277359680494</v>
       </c>
       <c r="C47">
-        <v>1439.985244070531</v>
+        <v>1297.743862980027</v>
       </c>
       <c r="D47">
-        <v>5234.55024407053</v>
+        <v>5178.905862980027</v>
       </c>
       <c r="E47">
-        <v>2349.065</v>
+        <v>2435.661999999999</v>
       </c>
       <c r="F47">
-        <v>3896.865</v>
+        <v>3983.462</v>
       </c>
       <c r="G47">
         <v>102.3</v>
@@ -5141,37 +5141,37 @@
         <v>336.1000000000001</v>
       </c>
       <c r="M47">
-        <v>782.490492</v>
+        <v>799.8791696</v>
       </c>
       <c r="N47">
-        <v>-446.3904919999999</v>
+        <v>-463.7791695999998</v>
       </c>
       <c r="O47">
-        <v>-142.84495744</v>
+        <v>-148.4093342719999</v>
       </c>
       <c r="P47">
-        <v>-303.5455345599999</v>
+        <v>-315.3698353279999</v>
       </c>
       <c r="Q47">
-        <v>1076.25446544</v>
+        <v>1064.430164672</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1155228468260011</v>
+        <v>0.1168140106561122</v>
       </c>
       <c r="T47">
-        <v>0.9087224261441427</v>
+        <v>0.925550619220886</v>
       </c>
       <c r="U47">
         <v>0.2008</v>
       </c>
       <c r="V47">
-        <v>0.1374483154742282</v>
+        <v>0.1344603086160928</v>
       </c>
       <c r="W47">
-        <v>0.173200378252775</v>
+        <v>0.1738003700298886</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>0.4295259858569631</v>
+        <v>0.42018846442529</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1430277359680494</v>
+        <v>0.1445777359680493</v>
       </c>
       <c r="C48">
-        <v>1297.743862980027</v>
+        <v>1156.673061562424</v>
       </c>
       <c r="D48">
-        <v>5178.905862980027</v>
+        <v>5124.432061562424</v>
       </c>
       <c r="E48">
-        <v>2435.661999999999</v>
+        <v>2522.259</v>
       </c>
       <c r="F48">
-        <v>3983.462</v>
+        <v>4070.059</v>
       </c>
       <c r="G48">
         <v>102.3</v>
@@ -5223,37 +5223,37 @@
         <v>336.1000000000001</v>
       </c>
       <c r="M48">
-        <v>799.8791696</v>
+        <v>817.2678472</v>
       </c>
       <c r="N48">
-        <v>-463.7791695999998</v>
+        <v>-481.1678471999999</v>
       </c>
       <c r="O48">
-        <v>-148.4093342719999</v>
+        <v>-153.973711104</v>
       </c>
       <c r="P48">
-        <v>-315.3698353279999</v>
+        <v>-327.1941360959999</v>
       </c>
       <c r="Q48">
-        <v>1064.430164672</v>
+        <v>1052.605863904</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1168140106561122</v>
+        <v>0.1181538976496238</v>
       </c>
       <c r="T48">
-        <v>0.925550619220886</v>
+        <v>0.9430138384514689</v>
       </c>
       <c r="U48">
         <v>0.2008</v>
       </c>
       <c r="V48">
-        <v>0.1344603086160928</v>
+        <v>0.1315994509859632</v>
       </c>
       <c r="W48">
-        <v>0.1738003700298886</v>
+        <v>0.1743748302420186</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>0.42018846442529</v>
+        <v>0.4112482843311349</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1445777359680493</v>
+        <v>0.1461277359680493</v>
       </c>
       <c r="C49">
-        <v>1156.673061562424</v>
+        <v>1016.736286426562</v>
       </c>
       <c r="D49">
-        <v>5124.432061562424</v>
+        <v>5071.092286426562</v>
       </c>
       <c r="E49">
-        <v>2522.259</v>
+        <v>2608.856</v>
       </c>
       <c r="F49">
-        <v>4070.059</v>
+        <v>4156.656</v>
       </c>
       <c r="G49">
         <v>102.3</v>
@@ -5305,37 +5305,37 @@
         <v>336.1000000000001</v>
       </c>
       <c r="M49">
-        <v>817.2678472</v>
+        <v>834.6565248000001</v>
       </c>
       <c r="N49">
-        <v>-481.1678471999999</v>
+        <v>-498.5565247999999</v>
       </c>
       <c r="O49">
-        <v>-153.973711104</v>
+        <v>-159.538087936</v>
       </c>
       <c r="P49">
-        <v>-327.1941360959999</v>
+        <v>-339.0184368639999</v>
       </c>
       <c r="Q49">
-        <v>1052.605863904</v>
+        <v>1040.781563136</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1181538976496238</v>
+        <v>0.1195453187582703</v>
       </c>
       <c r="T49">
-        <v>0.9430138384514689</v>
+        <v>0.9611487199601508</v>
       </c>
       <c r="U49">
         <v>0.2008</v>
       </c>
       <c r="V49">
-        <v>0.1315994509859632</v>
+        <v>0.1288577957570889</v>
       </c>
       <c r="W49">
-        <v>0.1743748302420186</v>
+        <v>0.1749253546119766</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.4112482843311349</v>
+        <v>0.402680611740903</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1461277359680493</v>
+        <v>0.1476777359680493</v>
       </c>
       <c r="C50">
-        <v>1016.736286426564</v>
+        <v>877.8984904273948</v>
       </c>
       <c r="D50">
-        <v>5071.092286426563</v>
+        <v>5018.851490427394</v>
       </c>
       <c r="E50">
-        <v>2608.855999999999</v>
+        <v>2695.453</v>
       </c>
       <c r="F50">
-        <v>4156.655999999999</v>
+        <v>4243.253</v>
       </c>
       <c r="G50">
         <v>102.3</v>
@@ -5387,37 +5387,37 @@
         <v>336.1000000000001</v>
       </c>
       <c r="M50">
-        <v>834.6565247999998</v>
+        <v>852.0452024</v>
       </c>
       <c r="N50">
-        <v>-498.5565247999997</v>
+        <v>-515.9452023999999</v>
       </c>
       <c r="O50">
-        <v>-159.5380879359999</v>
+        <v>-165.1024647679999</v>
       </c>
       <c r="P50">
-        <v>-339.0184368639998</v>
+        <v>-350.8427376319999</v>
       </c>
       <c r="Q50">
-        <v>1040.781563136</v>
+        <v>1028.957262368</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1195453187582703</v>
+        <v>0.1209913054005894</v>
       </c>
       <c r="T50">
-        <v>0.9611487199601508</v>
+        <v>0.9799947732927028</v>
       </c>
       <c r="U50">
         <v>0.2008</v>
       </c>
       <c r="V50">
-        <v>0.128857795757089</v>
+        <v>0.1262280448232708</v>
       </c>
       <c r="W50">
-        <v>0.1749253546119765</v>
+        <v>0.1754534085994872</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.4026806117409031</v>
+        <v>0.3944626400727212</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1476777359680493</v>
+        <v>0.1492277359680493</v>
       </c>
       <c r="C51">
-        <v>877.8984904273948</v>
+        <v>740.126055872709</v>
       </c>
       <c r="D51">
-        <v>5018.851490427394</v>
+        <v>4967.676055872708</v>
       </c>
       <c r="E51">
-        <v>2695.453</v>
+        <v>2782.049999999999</v>
       </c>
       <c r="F51">
-        <v>4243.253</v>
+        <v>4329.849999999999</v>
       </c>
       <c r="G51">
         <v>102.3</v>
@@ -5469,37 +5469,37 @@
         <v>336.1000000000001</v>
       </c>
       <c r="M51">
-        <v>852.0452024</v>
+        <v>869.4338799999999</v>
       </c>
       <c r="N51">
-        <v>-515.9452023999999</v>
+        <v>-533.3338799999998</v>
       </c>
       <c r="O51">
-        <v>-165.1024647679999</v>
+        <v>-170.6668415999999</v>
       </c>
       <c r="P51">
-        <v>-350.8427376319999</v>
+        <v>-362.6670383999999</v>
       </c>
       <c r="Q51">
-        <v>1028.957262368</v>
+        <v>1017.1329616</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1209913054005894</v>
+        <v>0.1224951315086012</v>
       </c>
       <c r="T51">
-        <v>0.9799947732927028</v>
+        <v>0.9995946687585568</v>
       </c>
       <c r="U51">
         <v>0.2008</v>
       </c>
       <c r="V51">
-        <v>0.1262280448232708</v>
+        <v>0.1237034839268054</v>
       </c>
       <c r="W51">
-        <v>0.1754534085994872</v>
+        <v>0.1759603404274975</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.3944626400727212</v>
+        <v>0.3865733872712669</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1492277359680493</v>
+        <v>0.1507777359680493</v>
       </c>
       <c r="C52">
-        <v>740.126055872709</v>
+        <v>603.3867223806456</v>
       </c>
       <c r="D52">
-        <v>4967.676055872708</v>
+        <v>4917.533722380645</v>
       </c>
       <c r="E52">
-        <v>2782.049999999999</v>
+        <v>2868.646999999999</v>
       </c>
       <c r="F52">
-        <v>4329.849999999999</v>
+        <v>4416.446999999999</v>
       </c>
       <c r="G52">
         <v>102.3</v>
@@ -5551,37 +5551,37 @@
         <v>336.1000000000001</v>
       </c>
       <c r="M52">
-        <v>869.4338799999999</v>
+        <v>886.8225575999999</v>
       </c>
       <c r="N52">
-        <v>-533.3338799999998</v>
+        <v>-550.7225575999997</v>
       </c>
       <c r="O52">
-        <v>-170.6668415999999</v>
+        <v>-176.2312184319999</v>
       </c>
       <c r="P52">
-        <v>-362.6670383999999</v>
+        <v>-374.4913391679999</v>
       </c>
       <c r="Q52">
-        <v>1017.1329616</v>
+        <v>1005.308660832</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1224951315086012</v>
+        <v>0.1240603382740828</v>
       </c>
       <c r="T52">
-        <v>0.9995946687585568</v>
+        <v>1.019994559957711</v>
       </c>
       <c r="U52">
         <v>0.2008</v>
       </c>
       <c r="V52">
-        <v>0.1237034839268054</v>
+        <v>0.1212779254184367</v>
       </c>
       <c r="W52">
-        <v>0.1759603404274975</v>
+        <v>0.1764473925759779</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.3865733872712669</v>
+        <v>0.3789935169326146</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1507777359680493</v>
+        <v>0.1523277359680494</v>
       </c>
       <c r="C53">
-        <v>603.3867223806456</v>
+        <v>467.6495190626647</v>
       </c>
       <c r="D53">
-        <v>4917.533722380645</v>
+        <v>4868.393519062664</v>
       </c>
       <c r="E53">
-        <v>2868.646999999999</v>
+        <v>2955.244</v>
       </c>
       <c r="F53">
-        <v>4416.446999999999</v>
+        <v>4503.044</v>
       </c>
       <c r="G53">
         <v>102.3</v>
@@ -5633,37 +5633,37 @@
         <v>336.1000000000001</v>
       </c>
       <c r="M53">
-        <v>886.8225575999999</v>
+        <v>904.2112352</v>
       </c>
       <c r="N53">
-        <v>-550.7225575999997</v>
+        <v>-568.1112351999999</v>
       </c>
       <c r="O53">
-        <v>-176.2312184319999</v>
+        <v>-181.795595264</v>
       </c>
       <c r="P53">
-        <v>-374.4913391679999</v>
+        <v>-386.3156399359999</v>
       </c>
       <c r="Q53">
-        <v>1005.308660832</v>
+        <v>993.484360064</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1240603382740828</v>
+        <v>0.1256907619881262</v>
       </c>
       <c r="T53">
-        <v>1.019994559957711</v>
+        <v>1.041244446623497</v>
       </c>
       <c r="U53">
         <v>0.2008</v>
       </c>
       <c r="V53">
-        <v>0.1212779254184367</v>
+        <v>0.1189456576219282</v>
       </c>
       <c r="W53">
-        <v>0.1764473925759779</v>
+        <v>0.1769157119495168</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.3789935169326146</v>
+        <v>0.3717051800685258</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1523277359680494</v>
+        <v>0.1538777359680493</v>
       </c>
       <c r="C54">
-        <v>467.6495190626647</v>
+        <v>332.8847007324093</v>
       </c>
       <c r="D54">
-        <v>4868.393519062664</v>
+        <v>4820.225700732409</v>
       </c>
       <c r="E54">
-        <v>2955.244</v>
+        <v>3041.840999999999</v>
       </c>
       <c r="F54">
-        <v>4503.044</v>
+        <v>4589.641</v>
       </c>
       <c r="G54">
         <v>102.3</v>
@@ -5715,37 +5715,37 @@
         <v>336.1000000000001</v>
       </c>
       <c r="M54">
-        <v>904.2112352</v>
+        <v>921.5999128</v>
       </c>
       <c r="N54">
-        <v>-568.1112351999999</v>
+        <v>-585.4999127999998</v>
       </c>
       <c r="O54">
-        <v>-181.795595264</v>
+        <v>-187.359972096</v>
       </c>
       <c r="P54">
-        <v>-386.3156399359999</v>
+        <v>-398.1399407039999</v>
       </c>
       <c r="Q54">
-        <v>993.484360064</v>
+        <v>981.6600592960001</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1256907619881262</v>
+        <v>0.1273905654346821</v>
       </c>
       <c r="T54">
-        <v>1.041244446623497</v>
+        <v>1.063398583785699</v>
       </c>
       <c r="U54">
         <v>0.2008</v>
       </c>
       <c r="V54">
-        <v>0.1189456576219282</v>
+        <v>0.1167013999309485</v>
       </c>
       <c r="W54">
-        <v>0.1769157119495168</v>
+        <v>0.1773663588938655</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.3717051800685258</v>
+        <v>0.3646918747842141</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1538777359680493</v>
+        <v>0.1554277359680493</v>
       </c>
       <c r="C55">
-        <v>332.8847007324093</v>
+        <v>199.0636878643363</v>
       </c>
       <c r="D55">
-        <v>4820.225700732409</v>
+        <v>4773.001687864336</v>
       </c>
       <c r="E55">
-        <v>3041.840999999999</v>
+        <v>3128.437999999999</v>
       </c>
       <c r="F55">
-        <v>4589.641</v>
+        <v>4676.237999999999</v>
       </c>
       <c r="G55">
         <v>102.3</v>
@@ -5797,37 +5797,37 @@
         <v>336.1000000000001</v>
       </c>
       <c r="M55">
-        <v>921.5999128</v>
+        <v>938.9885903999999</v>
       </c>
       <c r="N55">
-        <v>-585.4999127999998</v>
+        <v>-602.8885903999998</v>
       </c>
       <c r="O55">
-        <v>-187.359972096</v>
+        <v>-192.9243489279999</v>
       </c>
       <c r="P55">
-        <v>-398.1399407039999</v>
+        <v>-409.9642414719998</v>
       </c>
       <c r="Q55">
-        <v>981.6600592960001</v>
+        <v>969.8357585280002</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1273905654346821</v>
+        <v>0.1291642733789143</v>
       </c>
       <c r="T55">
-        <v>1.063398583785699</v>
+        <v>1.086515944302779</v>
       </c>
       <c r="U55">
         <v>0.2008</v>
       </c>
       <c r="V55">
-        <v>0.1167013999309485</v>
+        <v>0.1145402628951902</v>
       </c>
       <c r="W55">
-        <v>0.1773663588938655</v>
+        <v>0.1778003152106458</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.3646918747842141</v>
+        <v>0.3579383215474693</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1554277359680493</v>
+        <v>0.1569777359680493</v>
       </c>
       <c r="C56">
-        <v>199.0636878643363</v>
+        <v>66.15901004750413</v>
       </c>
       <c r="D56">
-        <v>4773.001687864336</v>
+        <v>4726.694010047504</v>
       </c>
       <c r="E56">
-        <v>3128.437999999999</v>
+        <v>3215.035</v>
       </c>
       <c r="F56">
-        <v>4676.237999999999</v>
+        <v>4762.835</v>
       </c>
       <c r="G56">
         <v>102.3</v>
@@ -5879,37 +5879,37 @@
         <v>336.1000000000001</v>
       </c>
       <c r="M56">
-        <v>938.9885903999999</v>
+        <v>956.3772680000001</v>
       </c>
       <c r="N56">
-        <v>-602.8885903999998</v>
+        <v>-620.2772679999999</v>
       </c>
       <c r="O56">
-        <v>-192.9243489279999</v>
+        <v>-198.48872576</v>
       </c>
       <c r="P56">
-        <v>-409.9642414719998</v>
+        <v>-421.78854224</v>
       </c>
       <c r="Q56">
-        <v>969.8357585280002</v>
+        <v>958.01145776</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1291642733789143</v>
+        <v>0.1310168127873346</v>
       </c>
       <c r="T56">
-        <v>1.086515944302779</v>
+        <v>1.110660743065063</v>
       </c>
       <c r="U56">
         <v>0.2008</v>
       </c>
       <c r="V56">
-        <v>0.1145402628951902</v>
+        <v>0.1124577126607322</v>
       </c>
       <c r="W56">
-        <v>0.1778003152106458</v>
+        <v>0.178218491297725</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.3579383215474693</v>
+        <v>0.351430352064788</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1569777359680493</v>
+        <v>0.1585277359680493</v>
       </c>
       <c r="C57">
-        <v>66.15901004750413</v>
+        <v>-65.85574730061489</v>
       </c>
       <c r="D57">
-        <v>4726.694010047504</v>
+        <v>4681.276252699385</v>
       </c>
       <c r="E57">
-        <v>3215.035</v>
+        <v>3301.632</v>
       </c>
       <c r="F57">
-        <v>4762.835</v>
+        <v>4849.432</v>
       </c>
       <c r="G57">
         <v>102.3</v>
@@ -5961,37 +5961,37 @@
         <v>336.1000000000001</v>
       </c>
       <c r="M57">
-        <v>956.3772680000001</v>
+        <v>973.7659456</v>
       </c>
       <c r="N57">
-        <v>-620.2772679999999</v>
+        <v>-637.6659455999999</v>
       </c>
       <c r="O57">
-        <v>-198.48872576</v>
+        <v>-204.053102592</v>
       </c>
       <c r="P57">
-        <v>-421.78854224</v>
+        <v>-433.6128430079999</v>
       </c>
       <c r="Q57">
-        <v>958.01145776</v>
+        <v>946.187156992</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1310168127873346</v>
+        <v>0.1329535585325013</v>
       </c>
       <c r="T57">
-        <v>1.110660743065063</v>
+        <v>1.135903032680178</v>
       </c>
       <c r="U57">
         <v>0.2008</v>
       </c>
       <c r="V57">
-        <v>0.1124577126607322</v>
+        <v>0.110449539220362</v>
       </c>
       <c r="W57">
-        <v>0.178218491297725</v>
+        <v>0.1786217325245513</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.351430352064788</v>
+        <v>0.3451548100636311</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1585277359680493</v>
+        <v>0.1600777359680493</v>
       </c>
       <c r="C58">
-        <v>-65.85574730061489</v>
+        <v>-197.0059931774695</v>
       </c>
       <c r="D58">
-        <v>4681.276252699385</v>
+        <v>4636.72300682253</v>
       </c>
       <c r="E58">
-        <v>3301.632</v>
+        <v>3388.228999999999</v>
       </c>
       <c r="F58">
-        <v>4849.432</v>
+        <v>4936.029</v>
       </c>
       <c r="G58">
         <v>102.3</v>
@@ -6043,37 +6043,37 @@
         <v>336.1000000000001</v>
       </c>
       <c r="M58">
-        <v>973.7659456</v>
+        <v>991.1546231999999</v>
       </c>
       <c r="N58">
-        <v>-637.6659455999999</v>
+        <v>-655.0546231999998</v>
       </c>
       <c r="O58">
-        <v>-204.053102592</v>
+        <v>-209.617479424</v>
       </c>
       <c r="P58">
-        <v>-433.6128430079999</v>
+        <v>-445.4371437759999</v>
       </c>
       <c r="Q58">
-        <v>946.187156992</v>
+        <v>934.3628562240001</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1329535585325013</v>
+        <v>0.1349803854751176</v>
       </c>
       <c r="T58">
-        <v>1.135903032680178</v>
+        <v>1.162319382277392</v>
       </c>
       <c r="U58">
         <v>0.2008</v>
       </c>
       <c r="V58">
-        <v>0.110449539220362</v>
+        <v>0.1085118280059696</v>
       </c>
       <c r="W58">
-        <v>0.1786217325245513</v>
+        <v>0.1790108249364013</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.3451548100636311</v>
+        <v>0.3390994625186551</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1600777359680493</v>
+        <v>0.1616277359680493</v>
       </c>
       <c r="C59">
-        <v>-197.0059931774695</v>
+        <v>-327.3161783967153</v>
       </c>
       <c r="D59">
-        <v>4636.72300682253</v>
+        <v>4593.009821603285</v>
       </c>
       <c r="E59">
-        <v>3388.228999999999</v>
+        <v>3474.826</v>
       </c>
       <c r="F59">
-        <v>4936.029</v>
+        <v>5022.626</v>
       </c>
       <c r="G59">
         <v>102.3</v>
@@ -6125,37 +6125,37 @@
         <v>336.1000000000001</v>
       </c>
       <c r="M59">
-        <v>991.1546231999999</v>
+        <v>1008.5433008</v>
       </c>
       <c r="N59">
-        <v>-655.0546231999998</v>
+        <v>-672.4433008</v>
       </c>
       <c r="O59">
-        <v>-209.617479424</v>
+        <v>-215.181856256</v>
       </c>
       <c r="P59">
-        <v>-445.4371437759999</v>
+        <v>-457.261444544</v>
       </c>
       <c r="Q59">
-        <v>934.3628562240001</v>
+        <v>922.538555456</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1349803854751176</v>
+        <v>0.13710372798643</v>
       </c>
       <c r="T59">
-        <v>1.162319382277392</v>
+        <v>1.189993653283997</v>
       </c>
       <c r="U59">
         <v>0.2008</v>
       </c>
       <c r="V59">
-        <v>0.1085118280059696</v>
+        <v>0.1066409344196598</v>
       </c>
       <c r="W59">
-        <v>0.1790108249364013</v>
+        <v>0.1793865003685323</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.3390994625186551</v>
+        <v>0.3332529200614369</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1616277359680493</v>
+        <v>0.1631777359680493</v>
       </c>
       <c r="C60">
-        <v>-327.3161783967143</v>
+        <v>-456.8098403332524</v>
       </c>
       <c r="D60">
-        <v>4593.009821603285</v>
+        <v>4550.113159666746</v>
       </c>
       <c r="E60">
-        <v>3474.825999999999</v>
+        <v>3561.422999999999</v>
       </c>
       <c r="F60">
-        <v>5022.625999999999</v>
+        <v>5109.222999999999</v>
       </c>
       <c r="G60">
         <v>102.3</v>
@@ -6207,37 +6207,37 @@
         <v>336.1000000000001</v>
       </c>
       <c r="M60">
-        <v>1008.5433008</v>
+        <v>1025.9319784</v>
       </c>
       <c r="N60">
-        <v>-672.4433007999997</v>
+        <v>-689.8319783999998</v>
       </c>
       <c r="O60">
-        <v>-215.1818562559999</v>
+        <v>-220.7462330879999</v>
       </c>
       <c r="P60">
-        <v>-457.2614445439998</v>
+        <v>-469.0857453119999</v>
       </c>
       <c r="Q60">
-        <v>922.5385554560002</v>
+        <v>910.7142546880001</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.13710372798643</v>
+        <v>0.1393306481812209</v>
       </c>
       <c r="T60">
-        <v>1.189993653283996</v>
+        <v>1.219017888729947</v>
       </c>
       <c r="U60">
         <v>0.2008</v>
       </c>
       <c r="V60">
-        <v>0.1066409344196598</v>
+        <v>0.1048334609549198</v>
       </c>
       <c r="W60">
-        <v>0.1793865003685323</v>
+        <v>0.1797494410402521</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.3332529200614369</v>
+        <v>0.3276045654841244</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1631777359680493</v>
+        <v>0.1647277359680493</v>
       </c>
       <c r="C61">
-        <v>-456.8098403332524</v>
+        <v>-585.5096451840927</v>
       </c>
       <c r="D61">
-        <v>4550.113159666746</v>
+        <v>4508.010354815906</v>
       </c>
       <c r="E61">
-        <v>3561.422999999999</v>
+        <v>3648.019999999999</v>
       </c>
       <c r="F61">
-        <v>5109.222999999999</v>
+        <v>5195.819999999999</v>
       </c>
       <c r="G61">
         <v>102.3</v>
@@ -6289,37 +6289,37 @@
         <v>336.1000000000001</v>
       </c>
       <c r="M61">
-        <v>1025.9319784</v>
+        <v>1043.320656</v>
       </c>
       <c r="N61">
-        <v>-689.8319783999998</v>
+        <v>-707.2206559999997</v>
       </c>
       <c r="O61">
-        <v>-220.7462330879999</v>
+        <v>-226.3106099199999</v>
       </c>
       <c r="P61">
-        <v>-469.0857453119999</v>
+        <v>-480.9100460799998</v>
       </c>
       <c r="Q61">
-        <v>910.7142546880001</v>
+        <v>898.8899539200002</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1393306481812209</v>
+        <v>0.1416689143857514</v>
       </c>
       <c r="T61">
-        <v>1.219017888729947</v>
+        <v>1.249493335948196</v>
       </c>
       <c r="U61">
         <v>0.2008</v>
       </c>
       <c r="V61">
-        <v>0.1048334609549198</v>
+        <v>0.1030862366056712</v>
       </c>
       <c r="W61">
-        <v>0.1797494410402521</v>
+        <v>0.1801002836895812</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.3276045654841244</v>
+        <v>0.3221444893927224</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1647277359680493</v>
+        <v>0.1662777359680493</v>
       </c>
       <c r="C62">
-        <v>-585.5096451840927</v>
+        <v>-713.4374279044396</v>
       </c>
       <c r="D62">
-        <v>4508.010354815906</v>
+        <v>4466.67957209556</v>
       </c>
       <c r="E62">
-        <v>3648.019999999999</v>
+        <v>3734.616999999999</v>
       </c>
       <c r="F62">
-        <v>5195.819999999999</v>
+        <v>5282.416999999999</v>
       </c>
       <c r="G62">
         <v>102.3</v>
@@ -6371,37 +6371,37 @@
         <v>336.1000000000001</v>
       </c>
       <c r="M62">
-        <v>1043.320656</v>
+        <v>1060.7093336</v>
       </c>
       <c r="N62">
-        <v>-707.2206559999997</v>
+        <v>-724.6093335999999</v>
       </c>
       <c r="O62">
-        <v>-226.3106099199999</v>
+        <v>-231.874986752</v>
       </c>
       <c r="P62">
-        <v>-480.9100460799998</v>
+        <v>-492.7343468479999</v>
       </c>
       <c r="Q62">
-        <v>898.8899539200002</v>
+        <v>887.0656531520001</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1416689143857514</v>
+        <v>0.1441270916776938</v>
       </c>
       <c r="T62">
-        <v>1.249493335948196</v>
+        <v>1.281531626613534</v>
       </c>
       <c r="U62">
         <v>0.2008</v>
       </c>
       <c r="V62">
-        <v>0.1030862366056712</v>
+        <v>0.1013962983006602</v>
       </c>
       <c r="W62">
-        <v>0.1801002836895812</v>
+        <v>0.1804396233012274</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.3221444893927224</v>
+        <v>0.3168634321895629</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1662777359680493</v>
+        <v>0.1678277359680493</v>
       </c>
       <c r="C63">
-        <v>-713.4374279044396</v>
+        <v>-840.6142299668709</v>
       </c>
       <c r="D63">
-        <v>4466.67957209556</v>
+        <v>4426.099770033128</v>
       </c>
       <c r="E63">
-        <v>3734.616999999999</v>
+        <v>3821.213999999999</v>
       </c>
       <c r="F63">
-        <v>5282.416999999999</v>
+        <v>5369.013999999999</v>
       </c>
       <c r="G63">
         <v>102.3</v>
@@ -6453,37 +6453,37 @@
         <v>336.1000000000001</v>
       </c>
       <c r="M63">
-        <v>1060.7093336</v>
+        <v>1078.0980112</v>
       </c>
       <c r="N63">
-        <v>-724.6093335999999</v>
+        <v>-741.9980111999998</v>
       </c>
       <c r="O63">
-        <v>-231.874986752</v>
+        <v>-237.4393635839999</v>
       </c>
       <c r="P63">
-        <v>-492.7343468479999</v>
+        <v>-504.5586476159999</v>
       </c>
       <c r="Q63">
-        <v>887.0656531520001</v>
+        <v>875.241352384</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1441270916776938</v>
+        <v>0.1467146467218436</v>
       </c>
       <c r="T63">
-        <v>1.281531626613534</v>
+        <v>1.315256143103364</v>
       </c>
       <c r="U63">
         <v>0.2008</v>
       </c>
       <c r="V63">
-        <v>0.1013962983006602</v>
+        <v>0.09976087413452048</v>
       </c>
       <c r="W63">
-        <v>0.1804396233012274</v>
+        <v>0.1807680164737883</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.3168634321895629</v>
+        <v>0.3117527316703765</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1678277359680493</v>
+        <v>0.1693777359680493</v>
       </c>
       <c r="C64">
-        <v>-840.6142299668709</v>
+        <v>-967.060335080786</v>
       </c>
       <c r="D64">
-        <v>4426.099770033128</v>
+        <v>4386.250664919213</v>
       </c>
       <c r="E64">
-        <v>3821.213999999999</v>
+        <v>3907.810999999999</v>
       </c>
       <c r="F64">
-        <v>5369.013999999999</v>
+        <v>5455.610999999999</v>
       </c>
       <c r="G64">
         <v>102.3</v>
@@ -6535,37 +6535,37 @@
         <v>336.1000000000001</v>
       </c>
       <c r="M64">
-        <v>1078.0980112</v>
+        <v>1095.4866888</v>
       </c>
       <c r="N64">
-        <v>-741.9980111999998</v>
+        <v>-759.3866887999998</v>
       </c>
       <c r="O64">
-        <v>-237.4393635839999</v>
+        <v>-243.0037404159999</v>
       </c>
       <c r="P64">
-        <v>-504.5586476159999</v>
+        <v>-516.3829483839999</v>
       </c>
       <c r="Q64">
-        <v>875.241352384</v>
+        <v>863.4170516160001</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1467146467218436</v>
+        <v>0.1494420696062178</v>
       </c>
       <c r="T64">
-        <v>1.315256143103364</v>
+        <v>1.350803606430482</v>
       </c>
       <c r="U64">
         <v>0.2008</v>
       </c>
       <c r="V64">
-        <v>0.09976087413452048</v>
+        <v>0.0981773681958773</v>
       </c>
       <c r="W64">
-        <v>0.1807680164737883</v>
+        <v>0.1810859844662678</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.3117527316703765</v>
+        <v>0.3068042756121165</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1693777359680493</v>
+        <v>0.1709277359680493</v>
       </c>
       <c r="C65">
-        <v>-967.060335080786</v>
+        <v>-1092.795302999553</v>
       </c>
       <c r="D65">
-        <v>4386.250664919213</v>
+        <v>4347.112697000446</v>
       </c>
       <c r="E65">
-        <v>3907.810999999999</v>
+        <v>3994.407999999999</v>
       </c>
       <c r="F65">
-        <v>5455.610999999999</v>
+        <v>5542.208</v>
       </c>
       <c r="G65">
         <v>102.3</v>
@@ -6617,37 +6617,37 @@
         <v>336.1000000000001</v>
       </c>
       <c r="M65">
-        <v>1095.4866888</v>
+        <v>1112.8753664</v>
       </c>
       <c r="N65">
-        <v>-759.3866887999998</v>
+        <v>-776.7753663999997</v>
       </c>
       <c r="O65">
-        <v>-243.0037404159999</v>
+        <v>-248.5681172479999</v>
       </c>
       <c r="P65">
-        <v>-516.3829483839999</v>
+        <v>-528.2072491519998</v>
       </c>
       <c r="Q65">
-        <v>863.4170516160001</v>
+        <v>851.5927508480002</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1494420696062178</v>
+        <v>0.1523210159841683</v>
       </c>
       <c r="T65">
-        <v>1.350803606430482</v>
+        <v>1.388325928831329</v>
       </c>
       <c r="U65">
         <v>0.2008</v>
       </c>
       <c r="V65">
-        <v>0.0981773681958773</v>
+        <v>0.09664334681781672</v>
       </c>
       <c r="W65">
-        <v>0.1810859844662678</v>
+        <v>0.1813940159589824</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.3068042756121165</v>
+        <v>0.3020104588056772</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1709277359680493</v>
+        <v>0.1724777359680493</v>
       </c>
       <c r="C66">
-        <v>-1092.795302999553</v>
+        <v>-1217.838001533684</v>
       </c>
       <c r="D66">
-        <v>4347.112697000446</v>
+        <v>4308.666998466315</v>
       </c>
       <c r="E66">
-        <v>3994.407999999999</v>
+        <v>4081.004999999999</v>
       </c>
       <c r="F66">
-        <v>5542.208</v>
+        <v>5628.804999999999</v>
       </c>
       <c r="G66">
         <v>102.3</v>
@@ -6699,37 +6699,37 @@
         <v>336.1000000000001</v>
       </c>
       <c r="M66">
-        <v>1112.8753664</v>
+        <v>1130.264044</v>
       </c>
       <c r="N66">
-        <v>-776.7753663999997</v>
+        <v>-794.1640439999999</v>
       </c>
       <c r="O66">
-        <v>-248.5681172479999</v>
+        <v>-254.13249408</v>
       </c>
       <c r="P66">
-        <v>-528.2072491519998</v>
+        <v>-540.0315499199999</v>
       </c>
       <c r="Q66">
-        <v>851.5927508480002</v>
+        <v>839.7684500800001</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1523210159841683</v>
+        <v>0.1553644735837159</v>
       </c>
       <c r="T66">
-        <v>1.388325928831329</v>
+        <v>1.427992383940796</v>
       </c>
       <c r="U66">
         <v>0.2008</v>
       </c>
       <c r="V66">
-        <v>0.09664334681781672</v>
+        <v>0.0951565260975426</v>
       </c>
       <c r="W66">
-        <v>0.1813940159589824</v>
+        <v>0.1816925695596134</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.3020104588056772</v>
+        <v>0.2973641440548206</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1724777359680493</v>
+        <v>0.1740277359680493</v>
       </c>
       <c r="C67">
-        <v>-1217.838001533684</v>
+        <v>-1342.206636880204</v>
       </c>
       <c r="D67">
-        <v>4308.666998466315</v>
+        <v>4270.895363119795</v>
       </c>
       <c r="E67">
-        <v>4081.004999999999</v>
+        <v>4167.601999999999</v>
       </c>
       <c r="F67">
-        <v>5628.804999999999</v>
+        <v>5715.401999999999</v>
       </c>
       <c r="G67">
         <v>102.3</v>
@@ -6781,37 +6781,37 @@
         <v>336.1000000000001</v>
       </c>
       <c r="M67">
-        <v>1130.264044</v>
+        <v>1147.6527216</v>
       </c>
       <c r="N67">
-        <v>-794.1640439999999</v>
+        <v>-811.5527215999998</v>
       </c>
       <c r="O67">
-        <v>-254.13249408</v>
+        <v>-259.696870912</v>
       </c>
       <c r="P67">
-        <v>-540.0315499199999</v>
+        <v>-551.8558506879999</v>
       </c>
       <c r="Q67">
-        <v>839.7684500800001</v>
+        <v>827.944149312</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1553644735837159</v>
+        <v>0.1585869581008841</v>
       </c>
       <c r="T67">
-        <v>1.427992383940796</v>
+        <v>1.469992159939054</v>
       </c>
       <c r="U67">
         <v>0.2008</v>
       </c>
       <c r="V67">
-        <v>0.0951565260975426</v>
+        <v>0.09371476055061015</v>
       </c>
       <c r="W67">
-        <v>0.1816925695596134</v>
+        <v>0.1819820760814375</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.2973641440548206</v>
+        <v>0.2928586267206567</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1740277359680493</v>
+        <v>0.1755777359680493</v>
       </c>
       <c r="C68">
-        <v>-1342.206636880204</v>
+        <v>-1465.918782370571</v>
       </c>
       <c r="D68">
-        <v>4270.895363119795</v>
+        <v>4233.780217629429</v>
       </c>
       <c r="E68">
-        <v>4167.601999999999</v>
+        <v>4254.199</v>
       </c>
       <c r="F68">
-        <v>5715.401999999999</v>
+        <v>5801.999</v>
       </c>
       <c r="G68">
         <v>102.3</v>
@@ -6863,37 +6863,37 @@
         <v>336.1000000000001</v>
       </c>
       <c r="M68">
-        <v>1147.6527216</v>
+        <v>1165.0413992</v>
       </c>
       <c r="N68">
-        <v>-811.5527215999998</v>
+        <v>-828.9413991999998</v>
       </c>
       <c r="O68">
-        <v>-259.696870912</v>
+        <v>-265.2612477439999</v>
       </c>
       <c r="P68">
-        <v>-551.8558506879999</v>
+        <v>-563.6801514559997</v>
       </c>
       <c r="Q68">
-        <v>827.944149312</v>
+        <v>816.1198485440002</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1585869581008841</v>
+        <v>0.1620047447100018</v>
       </c>
       <c r="T68">
-        <v>1.469992159939054</v>
+        <v>1.514537376906905</v>
       </c>
       <c r="U68">
         <v>0.2008</v>
       </c>
       <c r="V68">
-        <v>0.09371476055061015</v>
+        <v>0.09231603278119806</v>
       </c>
       <c r="W68">
-        <v>0.1819820760814375</v>
+        <v>0.1822629406175355</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.2928586267206567</v>
+        <v>0.2884876024412439</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1755777359680493</v>
+        <v>0.1771277359680493</v>
       </c>
       <c r="C69">
-        <v>-1465.918782370571</v>
+        <v>-1588.991405732555</v>
       </c>
       <c r="D69">
-        <v>4233.780217629429</v>
+        <v>4197.304594267444</v>
       </c>
       <c r="E69">
-        <v>4254.199</v>
+        <v>4340.795999999999</v>
       </c>
       <c r="F69">
-        <v>5801.999</v>
+        <v>5888.596</v>
       </c>
       <c r="G69">
         <v>102.3</v>
@@ -6945,37 +6945,37 @@
         <v>336.1000000000001</v>
       </c>
       <c r="M69">
-        <v>1165.0413992</v>
+        <v>1182.4300768</v>
       </c>
       <c r="N69">
-        <v>-828.9413991999998</v>
+        <v>-846.3300767999999</v>
       </c>
       <c r="O69">
-        <v>-265.2612477439999</v>
+        <v>-270.825624576</v>
       </c>
       <c r="P69">
-        <v>-563.6801514559997</v>
+        <v>-575.5044522239999</v>
       </c>
       <c r="Q69">
-        <v>816.1198485440002</v>
+        <v>804.295547776</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1620047447100018</v>
+        <v>0.1656361429821893</v>
       </c>
       <c r="T69">
-        <v>1.514537376906905</v>
+        <v>1.561866669935245</v>
       </c>
       <c r="U69">
         <v>0.2008</v>
       </c>
       <c r="V69">
-        <v>0.09231603278119806</v>
+        <v>0.0909584440638275</v>
       </c>
       <c r="W69">
-        <v>0.1822629406175355</v>
+        <v>0.1825355444319834</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.2884876024412439</v>
+        <v>0.2842451376994609</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1771277359680493</v>
+        <v>0.1786777359680493</v>
       </c>
       <c r="C70">
-        <v>-1588.991405732555</v>
+        <v>-1711.440894954954</v>
       </c>
       <c r="D70">
-        <v>4197.304594267444</v>
+        <v>4161.452105045045</v>
       </c>
       <c r="E70">
-        <v>4340.795999999999</v>
+        <v>4427.392999999999</v>
       </c>
       <c r="F70">
-        <v>5888.596</v>
+        <v>5975.192999999999</v>
       </c>
       <c r="G70">
         <v>102.3</v>
@@ -7027,37 +7027,37 @@
         <v>336.1000000000001</v>
       </c>
       <c r="M70">
-        <v>1182.4300768</v>
+        <v>1199.8187544</v>
       </c>
       <c r="N70">
-        <v>-846.3300767999999</v>
+        <v>-863.7187543999999</v>
       </c>
       <c r="O70">
-        <v>-270.825624576</v>
+        <v>-276.3900014079999</v>
       </c>
       <c r="P70">
-        <v>-575.5044522239999</v>
+        <v>-587.3287529919999</v>
       </c>
       <c r="Q70">
-        <v>804.295547776</v>
+        <v>792.4712470080001</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1656361429821893</v>
+        <v>0.1695018250138729</v>
       </c>
       <c r="T70">
-        <v>1.561866669935245</v>
+        <v>1.612249465739608</v>
       </c>
       <c r="U70">
         <v>0.2008</v>
       </c>
       <c r="V70">
-        <v>0.0909584440638275</v>
+        <v>0.08964020574406188</v>
       </c>
       <c r="W70">
-        <v>0.1825355444319834</v>
+        <v>0.1828002466865924</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.2842451376994609</v>
+        <v>0.2801256429501934</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1786777359680493</v>
+        <v>0.1802277359680493</v>
       </c>
       <c r="C71">
-        <v>-1711.440894954954</v>
+        <v>-1833.283082837909</v>
       </c>
       <c r="D71">
-        <v>4161.452105045045</v>
+        <v>4126.206917162091</v>
       </c>
       <c r="E71">
-        <v>4427.392999999999</v>
+        <v>4513.99</v>
       </c>
       <c r="F71">
-        <v>5975.192999999999</v>
+        <v>6061.79</v>
       </c>
       <c r="G71">
         <v>102.3</v>
@@ -7109,37 +7109,37 @@
         <v>336.1000000000001</v>
       </c>
       <c r="M71">
-        <v>1199.8187544</v>
+        <v>1217.207432</v>
       </c>
       <c r="N71">
-        <v>-863.7187543999999</v>
+        <v>-881.1074319999998</v>
       </c>
       <c r="O71">
-        <v>-276.3900014079999</v>
+        <v>-281.9543782399999</v>
       </c>
       <c r="P71">
-        <v>-587.3287529919999</v>
+        <v>-599.1530537599999</v>
       </c>
       <c r="Q71">
-        <v>792.4712470080001</v>
+        <v>780.64694624</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1695018250138729</v>
+        <v>0.173625219181002</v>
       </c>
       <c r="T71">
-        <v>1.612249465739608</v>
+        <v>1.665991114597595</v>
       </c>
       <c r="U71">
         <v>0.2008</v>
       </c>
       <c r="V71">
-        <v>0.08964020574406188</v>
+        <v>0.08835963137628956</v>
       </c>
       <c r="W71">
-        <v>0.1828002466865924</v>
+        <v>0.1830573860196411</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.2801256429501934</v>
+        <v>0.276123848050905</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1802277359680493</v>
+        <v>0.1817777359680493</v>
       </c>
       <c r="C72">
-        <v>-1833.283082837909</v>
+        <v>-1954.533270306158</v>
       </c>
       <c r="D72">
-        <v>4126.206917162091</v>
+        <v>4091.553729693842</v>
       </c>
       <c r="E72">
-        <v>4513.99</v>
+        <v>4600.587</v>
       </c>
       <c r="F72">
-        <v>6061.79</v>
+        <v>6148.387</v>
       </c>
       <c r="G72">
         <v>102.3</v>
@@ -7191,37 +7191,37 @@
         <v>336.1000000000001</v>
       </c>
       <c r="M72">
-        <v>1217.207432</v>
+        <v>1234.5961096</v>
       </c>
       <c r="N72">
-        <v>-881.1074319999998</v>
+        <v>-898.4961096</v>
       </c>
       <c r="O72">
-        <v>-281.9543782399999</v>
+        <v>-287.518755072</v>
       </c>
       <c r="P72">
-        <v>-599.1530537599999</v>
+        <v>-610.977354528</v>
       </c>
       <c r="Q72">
-        <v>780.64694624</v>
+        <v>768.822645472</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.173625219181002</v>
+        <v>0.1780329853596572</v>
       </c>
       <c r="T72">
-        <v>1.665991114597595</v>
+        <v>1.723439084066478</v>
       </c>
       <c r="U72">
         <v>0.2008</v>
       </c>
       <c r="V72">
-        <v>0.08835963137628956</v>
+        <v>0.08711512952591928</v>
       </c>
       <c r="W72">
-        <v>0.1830573860196411</v>
+        <v>0.1833072819911954</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.276123848050905</v>
+        <v>0.2722347797684977</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1817777359680493</v>
+        <v>0.1833277359680493</v>
       </c>
       <c r="C73">
-        <v>-1954.533270306157</v>
+        <v>-2075.206248557313</v>
       </c>
       <c r="D73">
-        <v>4091.553729693842</v>
+        <v>4057.477751442685</v>
       </c>
       <c r="E73">
-        <v>4600.586999999999</v>
+        <v>4687.183999999998</v>
       </c>
       <c r="F73">
-        <v>6148.386999999999</v>
+        <v>6234.983999999999</v>
       </c>
       <c r="G73">
         <v>102.3</v>
@@ -7273,37 +7273,37 @@
         <v>336.1000000000001</v>
       </c>
       <c r="M73">
-        <v>1234.5961096</v>
+        <v>1251.9847872</v>
       </c>
       <c r="N73">
-        <v>-898.4961095999997</v>
+        <v>-915.8847871999997</v>
       </c>
       <c r="O73">
-        <v>-287.5187550719999</v>
+        <v>-293.0831319039999</v>
       </c>
       <c r="P73">
-        <v>-610.9773545279998</v>
+        <v>-622.8016552959998</v>
       </c>
       <c r="Q73">
-        <v>768.8226454720002</v>
+        <v>756.9983447040001</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1780329853596572</v>
+        <v>0.1827555919796449</v>
       </c>
       <c r="T73">
-        <v>1.723439084066477</v>
+        <v>1.784990479925994</v>
       </c>
       <c r="U73">
         <v>0.2008</v>
       </c>
       <c r="V73">
-        <v>0.08711512952591929</v>
+        <v>0.08590519717139264</v>
       </c>
       <c r="W73">
-        <v>0.1833072819911954</v>
+        <v>0.1835502364079843</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.2722347797684977</v>
+        <v>0.2684537411606021</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1833277359680493</v>
+        <v>0.1848777359680493</v>
       </c>
       <c r="C74">
-        <v>-2075.206248557313</v>
+        <v>-2195.316320112537</v>
       </c>
       <c r="D74">
-        <v>4057.477751442685</v>
+        <v>4023.964679887462</v>
       </c>
       <c r="E74">
-        <v>4687.183999999998</v>
+        <v>4773.780999999999</v>
       </c>
       <c r="F74">
-        <v>6234.983999999999</v>
+        <v>6321.580999999999</v>
       </c>
       <c r="G74">
         <v>102.3</v>
@@ -7355,37 +7355,37 @@
         <v>336.1000000000001</v>
       </c>
       <c r="M74">
-        <v>1251.9847872</v>
+        <v>1269.3734648</v>
       </c>
       <c r="N74">
-        <v>-915.8847871999997</v>
+        <v>-933.2734647999998</v>
       </c>
       <c r="O74">
-        <v>-293.0831319039999</v>
+        <v>-298.647508736</v>
       </c>
       <c r="P74">
-        <v>-622.8016552959998</v>
+        <v>-634.6259560639999</v>
       </c>
       <c r="Q74">
-        <v>756.9983447040001</v>
+        <v>745.1740439360001</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1827555919796449</v>
+        <v>0.1878280213122244</v>
       </c>
       <c r="T74">
-        <v>1.784990479925994</v>
+        <v>1.851101238441772</v>
       </c>
       <c r="U74">
         <v>0.2008</v>
       </c>
       <c r="V74">
-        <v>0.08590519717139264</v>
+        <v>0.08472841364849684</v>
       </c>
       <c r="W74">
-        <v>0.1835502364079843</v>
+        <v>0.1837865345393818</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.2684537411606021</v>
+        <v>0.2647762926515527</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1848777359680493</v>
+        <v>0.1864277359680493</v>
       </c>
       <c r="C75">
-        <v>-2195.316320112537</v>
+        <v>-2314.877318832519</v>
       </c>
       <c r="D75">
-        <v>4023.964679887462</v>
+        <v>3991.00068116748</v>
       </c>
       <c r="E75">
-        <v>4773.780999999999</v>
+        <v>4860.377999999999</v>
       </c>
       <c r="F75">
-        <v>6321.580999999999</v>
+        <v>6408.177999999999</v>
       </c>
       <c r="G75">
         <v>102.3</v>
@@ -7437,37 +7437,37 @@
         <v>336.1000000000001</v>
       </c>
       <c r="M75">
-        <v>1269.3734648</v>
+        <v>1286.7621424</v>
       </c>
       <c r="N75">
-        <v>-933.2734647999998</v>
+        <v>-950.6621423999998</v>
       </c>
       <c r="O75">
-        <v>-298.647508736</v>
+        <v>-304.211885568</v>
       </c>
       <c r="P75">
-        <v>-634.6259560639999</v>
+        <v>-646.4502568319998</v>
       </c>
       <c r="Q75">
-        <v>745.1740439360001</v>
+        <v>733.3497431680001</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1878280213122244</v>
+        <v>0.1932906375165407</v>
       </c>
       <c r="T75">
-        <v>1.851101238441772</v>
+        <v>1.922297439920301</v>
       </c>
       <c r="U75">
         <v>0.2008</v>
       </c>
       <c r="V75">
-        <v>0.08472841364849684</v>
+        <v>0.08358343508567932</v>
       </c>
       <c r="W75">
-        <v>0.1837865345393818</v>
+        <v>0.1840164462347956</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.2647762926515527</v>
+        <v>0.2611982346427478</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1864277359680493</v>
+        <v>0.1879777359680493</v>
       </c>
       <c r="C76">
-        <v>-2314.877318832519</v>
+        <v>-2433.902628957656</v>
       </c>
       <c r="D76">
-        <v>3991.00068116748</v>
+        <v>3958.572371042343</v>
       </c>
       <c r="E76">
-        <v>4860.377999999999</v>
+        <v>4946.974999999999</v>
       </c>
       <c r="F76">
-        <v>6408.177999999999</v>
+        <v>6494.775</v>
       </c>
       <c r="G76">
         <v>102.3</v>
@@ -7519,37 +7519,37 @@
         <v>336.1000000000001</v>
       </c>
       <c r="M76">
-        <v>1286.7621424</v>
+        <v>1304.15082</v>
       </c>
       <c r="N76">
-        <v>-950.6621423999998</v>
+        <v>-968.0508199999999</v>
       </c>
       <c r="O76">
-        <v>-304.211885568</v>
+        <v>-309.7762624</v>
       </c>
       <c r="P76">
-        <v>-646.4502568319998</v>
+        <v>-658.2745576</v>
       </c>
       <c r="Q76">
-        <v>733.3497431680001</v>
+        <v>721.5254424</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1932906375165407</v>
+        <v>0.1991902630172023</v>
       </c>
       <c r="T76">
-        <v>1.922297439920301</v>
+        <v>1.999189337517114</v>
       </c>
       <c r="U76">
         <v>0.2008</v>
       </c>
       <c r="V76">
-        <v>0.08358343508567932</v>
+        <v>0.08246898928453693</v>
       </c>
       <c r="W76">
-        <v>0.1840164462347956</v>
+        <v>0.184240226951665</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.2611982346427478</v>
+        <v>0.2577155915141779</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1879777359680493</v>
+        <v>0.1895277359680493</v>
       </c>
       <c r="C77">
-        <v>-2433.902628957656</v>
+        <v>-2552.40520322746</v>
       </c>
       <c r="D77">
-        <v>3958.572371042343</v>
+        <v>3926.666796772539</v>
       </c>
       <c r="E77">
-        <v>4946.974999999999</v>
+        <v>5033.571999999999</v>
       </c>
       <c r="F77">
-        <v>6494.775</v>
+        <v>6581.371999999999</v>
       </c>
       <c r="G77">
         <v>102.3</v>
@@ -7601,37 +7601,37 @@
         <v>336.1000000000001</v>
       </c>
       <c r="M77">
-        <v>1304.15082</v>
+        <v>1321.5394976</v>
       </c>
       <c r="N77">
-        <v>-968.0508199999999</v>
+        <v>-985.4394975999999</v>
       </c>
       <c r="O77">
-        <v>-309.7762624</v>
+        <v>-315.3406392319999</v>
       </c>
       <c r="P77">
-        <v>-658.2745576</v>
+        <v>-670.0988583679999</v>
       </c>
       <c r="Q77">
-        <v>721.5254424</v>
+        <v>709.701141632</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1991902630172023</v>
+        <v>0.2055815239762525</v>
       </c>
       <c r="T77">
-        <v>1.999189337517114</v>
+        <v>2.082488893246994</v>
       </c>
       <c r="U77">
         <v>0.2008</v>
       </c>
       <c r="V77">
-        <v>0.08246898928453693</v>
+        <v>0.08138387100447723</v>
       </c>
       <c r="W77">
-        <v>0.184240226951665</v>
+        <v>0.184458118702301</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.2577155915141779</v>
+        <v>0.2543245968889913</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1895277359680493</v>
+        <v>0.1910777359680493</v>
       </c>
       <c r="C78">
-        <v>-2552.40520322746</v>
+        <v>-2670.397580130714</v>
       </c>
       <c r="D78">
-        <v>3926.666796772539</v>
+        <v>3895.271419869285</v>
       </c>
       <c r="E78">
-        <v>5033.571999999999</v>
+        <v>5120.168999999999</v>
       </c>
       <c r="F78">
-        <v>6581.371999999999</v>
+        <v>6667.968999999999</v>
       </c>
       <c r="G78">
         <v>102.3</v>
@@ -7683,37 +7683,37 @@
         <v>336.1000000000001</v>
       </c>
       <c r="M78">
-        <v>1321.5394976</v>
+        <v>1338.9281752</v>
       </c>
       <c r="N78">
-        <v>-985.4394975999999</v>
+        <v>-1002.8281752</v>
       </c>
       <c r="O78">
-        <v>-315.3406392319999</v>
+        <v>-320.9050160639999</v>
       </c>
       <c r="P78">
-        <v>-670.0988583679999</v>
+        <v>-681.9231591359999</v>
       </c>
       <c r="Q78">
-        <v>709.701141632</v>
+        <v>697.8768408640001</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2055815239762525</v>
+        <v>0.2125285467578287</v>
       </c>
       <c r="T78">
-        <v>2.082488893246994</v>
+        <v>2.173031888605559</v>
       </c>
       <c r="U78">
         <v>0.2008</v>
       </c>
       <c r="V78">
-        <v>0.08138387100447723</v>
+        <v>0.08032693761480869</v>
       </c>
       <c r="W78">
-        <v>0.184458118702301</v>
+        <v>0.1846703509269464</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.2543245968889913</v>
+        <v>0.2510216800462772</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1910777359680493</v>
+        <v>0.1926277359680493</v>
       </c>
       <c r="C79">
-        <v>-2670.397580130714</v>
+        <v>-2787.89190033468</v>
       </c>
       <c r="D79">
-        <v>3895.271419869285</v>
+        <v>3864.374099665319</v>
       </c>
       <c r="E79">
-        <v>5120.168999999999</v>
+        <v>5206.766</v>
       </c>
       <c r="F79">
-        <v>6667.968999999999</v>
+        <v>6754.566</v>
       </c>
       <c r="G79">
         <v>102.3</v>
@@ -7765,37 +7765,37 @@
         <v>336.1000000000001</v>
       </c>
       <c r="M79">
-        <v>1338.9281752</v>
+        <v>1356.3168528</v>
       </c>
       <c r="N79">
-        <v>-1002.8281752</v>
+        <v>-1020.2168528</v>
       </c>
       <c r="O79">
-        <v>-320.9050160639999</v>
+        <v>-326.469392896</v>
       </c>
       <c r="P79">
-        <v>-681.9231591359999</v>
+        <v>-693.7474599039999</v>
       </c>
       <c r="Q79">
-        <v>697.8768408640001</v>
+        <v>686.052540096</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2125285467578287</v>
+        <v>0.2201071170650027</v>
       </c>
       <c r="T79">
-        <v>2.173031888605559</v>
+        <v>2.271806065360356</v>
       </c>
       <c r="U79">
         <v>0.2008</v>
       </c>
       <c r="V79">
-        <v>0.08032693761480869</v>
+        <v>0.0792971050812855</v>
       </c>
       <c r="W79">
-        <v>0.1846703509269464</v>
+        <v>0.1848771412996779</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.2510216800462772</v>
+        <v>0.2478034533790172</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1926277359680493</v>
+        <v>0.1941777359680493</v>
       </c>
       <c r="C80">
-        <v>-2787.89190033468</v>
+        <v>-2904.89992233855</v>
       </c>
       <c r="D80">
-        <v>3864.374099665319</v>
+        <v>3833.963077661449</v>
       </c>
       <c r="E80">
-        <v>5206.766</v>
+        <v>5293.362999999999</v>
       </c>
       <c r="F80">
-        <v>6754.566</v>
+        <v>6841.163</v>
       </c>
       <c r="G80">
         <v>102.3</v>
@@ -7847,37 +7847,37 @@
         <v>336.1000000000001</v>
       </c>
       <c r="M80">
-        <v>1356.3168528</v>
+        <v>1373.7055304</v>
       </c>
       <c r="N80">
-        <v>-1020.2168528</v>
+        <v>-1037.6055304</v>
       </c>
       <c r="O80">
-        <v>-326.469392896</v>
+        <v>-332.033769728</v>
       </c>
       <c r="P80">
-        <v>-693.7474599039999</v>
+        <v>-705.571760672</v>
       </c>
       <c r="Q80">
-        <v>686.052540096</v>
+        <v>674.228239328</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2201071170650027</v>
+        <v>0.22840745597286</v>
       </c>
       <c r="T80">
-        <v>2.271806065360356</v>
+        <v>2.379987306567993</v>
       </c>
       <c r="U80">
         <v>0.2008</v>
       </c>
       <c r="V80">
-        <v>0.0792971050812855</v>
+        <v>0.07829334425747177</v>
       </c>
       <c r="W80">
-        <v>0.1848771412996779</v>
+        <v>0.1850786964730997</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.2478034533790172</v>
+        <v>0.2446667008045993</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1941777359680493</v>
+        <v>0.1957277359680493</v>
       </c>
       <c r="C81">
-        <v>-2904.89992233855</v>
+        <v>-3021.433037393549</v>
       </c>
       <c r="D81">
-        <v>3833.963077661449</v>
+        <v>3804.026962606451</v>
       </c>
       <c r="E81">
-        <v>5293.362999999999</v>
+        <v>5379.959999999999</v>
       </c>
       <c r="F81">
-        <v>6841.163</v>
+        <v>6927.759999999999</v>
       </c>
       <c r="G81">
         <v>102.3</v>
@@ -7929,37 +7929,37 @@
         <v>336.1000000000001</v>
       </c>
       <c r="M81">
-        <v>1373.7055304</v>
+        <v>1391.094208</v>
       </c>
       <c r="N81">
-        <v>-1037.6055304</v>
+        <v>-1054.994208</v>
       </c>
       <c r="O81">
-        <v>-332.033769728</v>
+        <v>-337.59814656</v>
       </c>
       <c r="P81">
-        <v>-705.571760672</v>
+        <v>-717.3960614399998</v>
       </c>
       <c r="Q81">
-        <v>674.228239328</v>
+        <v>662.4039385600001</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.22840745597286</v>
+        <v>0.237537828771503</v>
       </c>
       <c r="T81">
-        <v>2.379987306567993</v>
+        <v>2.498986671896393</v>
       </c>
       <c r="U81">
         <v>0.2008</v>
       </c>
       <c r="V81">
-        <v>0.07829334425747177</v>
+        <v>0.07731467745425337</v>
       </c>
       <c r="W81">
-        <v>0.1850786964730997</v>
+        <v>0.1852752127671859</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.2446667008045993</v>
+        <v>0.2416083670445418</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.1957277359680493</v>
+        <v>0.1972777359680493</v>
       </c>
       <c r="C82">
-        <v>-3021.433037393549</v>
+        <v>-3137.50228372947</v>
       </c>
       <c r="D82">
-        <v>3804.026962606451</v>
+        <v>3774.55471627053</v>
       </c>
       <c r="E82">
-        <v>5379.959999999999</v>
+        <v>5466.557</v>
       </c>
       <c r="F82">
-        <v>6927.759999999999</v>
+        <v>7014.357</v>
       </c>
       <c r="G82">
         <v>102.3</v>
@@ -8011,37 +8011,37 @@
         <v>336.1000000000001</v>
       </c>
       <c r="M82">
-        <v>1391.094208</v>
+        <v>1408.4828856</v>
       </c>
       <c r="N82">
-        <v>-1054.994208</v>
+        <v>-1072.3828856</v>
       </c>
       <c r="O82">
-        <v>-337.59814656</v>
+        <v>-343.162523392</v>
       </c>
       <c r="P82">
-        <v>-717.3960614399998</v>
+        <v>-729.220362208</v>
       </c>
       <c r="Q82">
-        <v>662.4039385600001</v>
+        <v>650.579637792</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.237537828771503</v>
+        <v>0.2476292934436873</v>
       </c>
       <c r="T82">
-        <v>2.498986671896393</v>
+        <v>2.630512286206729</v>
       </c>
       <c r="U82">
         <v>0.2008</v>
       </c>
       <c r="V82">
-        <v>0.07731467745425337</v>
+        <v>0.07636017526346012</v>
       </c>
       <c r="W82">
-        <v>0.1852752127671859</v>
+        <v>0.1854668768070972</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.2416083670445418</v>
+        <v>0.2386255476983128</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1972777359680493</v>
+        <v>0.1988277359680494</v>
       </c>
       <c r="C83">
-        <v>-3137.50228372947</v>
+        <v>-3253.118360124957</v>
       </c>
       <c r="D83">
-        <v>3774.55471627053</v>
+        <v>3745.535639875042</v>
       </c>
       <c r="E83">
-        <v>5466.557</v>
+        <v>5553.154</v>
       </c>
       <c r="F83">
-        <v>7014.357</v>
+        <v>7100.954</v>
       </c>
       <c r="G83">
         <v>102.3</v>
@@ -8093,37 +8093,37 @@
         <v>336.1000000000001</v>
       </c>
       <c r="M83">
-        <v>1408.4828856</v>
+        <v>1425.8715632</v>
       </c>
       <c r="N83">
-        <v>-1072.3828856</v>
+        <v>-1089.7715632</v>
       </c>
       <c r="O83">
-        <v>-343.162523392</v>
+        <v>-348.726900224</v>
       </c>
       <c r="P83">
-        <v>-729.220362208</v>
+        <v>-741.0446629759999</v>
       </c>
       <c r="Q83">
-        <v>650.579637792</v>
+        <v>638.755337024</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2476292934436873</v>
+        <v>0.2588420319683367</v>
       </c>
       <c r="T83">
-        <v>2.630512286206729</v>
+        <v>2.776651857662659</v>
       </c>
       <c r="U83">
         <v>0.2008</v>
       </c>
       <c r="V83">
-        <v>0.07636017526346012</v>
+        <v>0.07542895361390572</v>
       </c>
       <c r="W83">
-        <v>0.1854668768070972</v>
+        <v>0.1856538661143277</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.2386255476983128</v>
+        <v>0.2357154800434553</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1988277359680494</v>
+        <v>0.2003777359680493</v>
       </c>
       <c r="C84">
-        <v>-3253.118360124957</v>
+        <v>-3368.291638856588</v>
       </c>
       <c r="D84">
-        <v>3745.535639875042</v>
+        <v>3716.959361143412</v>
       </c>
       <c r="E84">
-        <v>5553.154</v>
+        <v>5639.750999999999</v>
       </c>
       <c r="F84">
-        <v>7100.954</v>
+        <v>7187.550999999999</v>
       </c>
       <c r="G84">
         <v>102.3</v>
@@ -8175,37 +8175,37 @@
         <v>336.1000000000001</v>
       </c>
       <c r="M84">
-        <v>1425.8715632</v>
+        <v>1443.2602408</v>
       </c>
       <c r="N84">
-        <v>-1089.7715632</v>
+        <v>-1107.1602408</v>
       </c>
       <c r="O84">
-        <v>-348.726900224</v>
+        <v>-354.291277056</v>
       </c>
       <c r="P84">
-        <v>-741.0446629759999</v>
+        <v>-752.868963744</v>
       </c>
       <c r="Q84">
-        <v>638.755337024</v>
+        <v>626.931036256</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2588420319683367</v>
+        <v>0.2713739162017682</v>
       </c>
       <c r="T84">
-        <v>2.776651857662659</v>
+        <v>2.939984319878109</v>
       </c>
       <c r="U84">
         <v>0.2008</v>
       </c>
       <c r="V84">
-        <v>0.07542895361390572</v>
+        <v>0.07452017104024421</v>
       </c>
       <c r="W84">
-        <v>0.1856538661143277</v>
+        <v>0.185836349655119</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.2357154800434553</v>
+        <v>0.2328755345007631</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2003777359680493</v>
+        <v>0.2019277359680494</v>
       </c>
       <c r="C85">
-        <v>-3368.291638856588</v>
+        <v>-3483.032178059686</v>
       </c>
       <c r="D85">
-        <v>3716.959361143412</v>
+        <v>3688.815821940314</v>
       </c>
       <c r="E85">
-        <v>5639.750999999999</v>
+        <v>5726.348</v>
       </c>
       <c r="F85">
-        <v>7187.550999999999</v>
+        <v>7274.148</v>
       </c>
       <c r="G85">
         <v>102.3</v>
@@ -8257,37 +8257,37 @@
         <v>336.1000000000001</v>
       </c>
       <c r="M85">
-        <v>1443.2602408</v>
+        <v>1460.6489184</v>
       </c>
       <c r="N85">
-        <v>-1107.1602408</v>
+        <v>-1124.5489184</v>
       </c>
       <c r="O85">
-        <v>-354.291277056</v>
+        <v>-359.855653888</v>
       </c>
       <c r="P85">
-        <v>-752.868963744</v>
+        <v>-764.693264512</v>
       </c>
       <c r="Q85">
-        <v>626.931036256</v>
+        <v>615.1067354879999</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2713739162017682</v>
+        <v>0.2854722859643788</v>
       </c>
       <c r="T85">
-        <v>2.939984319878109</v>
+        <v>3.123733339870492</v>
       </c>
       <c r="U85">
         <v>0.2008</v>
       </c>
       <c r="V85">
-        <v>0.07452017104024421</v>
+        <v>0.07363302614690796</v>
       </c>
       <c r="W85">
-        <v>0.185836349655119</v>
+        <v>0.1860144883497009</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.2328755345007631</v>
+        <v>0.2301032067090873</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2019277359680493</v>
+        <v>0.2034777359680493</v>
       </c>
       <c r="C86">
-        <v>-3483.032178059683</v>
+        <v>-3597.349733531784</v>
       </c>
       <c r="D86">
-        <v>3688.815821940316</v>
+        <v>3661.095266468215</v>
       </c>
       <c r="E86">
-        <v>5726.347999999999</v>
+        <v>5812.944999999999</v>
       </c>
       <c r="F86">
-        <v>7274.147999999999</v>
+        <v>7360.744999999999</v>
       </c>
       <c r="G86">
         <v>102.3</v>
@@ -8339,37 +8339,37 @@
         <v>336.1000000000001</v>
       </c>
       <c r="M86">
-        <v>1460.6489184</v>
+        <v>1478.037596</v>
       </c>
       <c r="N86">
-        <v>-1124.5489184</v>
+        <v>-1141.937596</v>
       </c>
       <c r="O86">
-        <v>-359.8556538879999</v>
+        <v>-365.4200307199999</v>
       </c>
       <c r="P86">
-        <v>-764.6932645119998</v>
+        <v>-776.5175652799999</v>
       </c>
       <c r="Q86">
-        <v>615.1067354880001</v>
+        <v>603.2824347200001</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2854722859643786</v>
+        <v>0.3014504383620039</v>
       </c>
       <c r="T86">
-        <v>3.12373333987049</v>
+        <v>3.331982229195189</v>
       </c>
       <c r="U86">
         <v>0.2008</v>
       </c>
       <c r="V86">
-        <v>0.07363302614690798</v>
+        <v>0.07276675525106199</v>
       </c>
       <c r="W86">
-        <v>0.1860144883497009</v>
+        <v>0.1861884355455868</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.2301032067090875</v>
+        <v>0.2273961101595687</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2034777359680493</v>
+        <v>0.2050277359680494</v>
       </c>
       <c r="C87">
-        <v>-3597.349733531784</v>
+        <v>-3711.253770007891</v>
       </c>
       <c r="D87">
-        <v>3661.095266468215</v>
+        <v>3633.788229992108</v>
       </c>
       <c r="E87">
-        <v>5812.944999999999</v>
+        <v>5899.541999999999</v>
       </c>
       <c r="F87">
-        <v>7360.744999999999</v>
+        <v>7447.341999999999</v>
       </c>
       <c r="G87">
         <v>102.3</v>
@@ -8421,37 +8421,37 @@
         <v>336.1000000000001</v>
       </c>
       <c r="M87">
-        <v>1478.037596</v>
+        <v>1495.4262736</v>
       </c>
       <c r="N87">
-        <v>-1141.937596</v>
+        <v>-1159.3262736</v>
       </c>
       <c r="O87">
-        <v>-365.4200307199999</v>
+        <v>-370.9844075519999</v>
       </c>
       <c r="P87">
-        <v>-776.5175652799999</v>
+        <v>-788.3418660479997</v>
       </c>
       <c r="Q87">
-        <v>603.2824347200001</v>
+        <v>591.4581339520003</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.3014504383620039</v>
+        <v>0.3197111839592899</v>
       </c>
       <c r="T87">
-        <v>3.331982229195189</v>
+        <v>3.569980959851989</v>
       </c>
       <c r="U87">
         <v>0.2008</v>
       </c>
       <c r="V87">
-        <v>0.07276675525106199</v>
+        <v>0.07192063019000315</v>
       </c>
       <c r="W87">
-        <v>0.1861884355455868</v>
+        <v>0.1863583374578474</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.2273961101595687</v>
+        <v>0.2247519693437598</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2050277359680494</v>
+        <v>0.2065777359680493</v>
       </c>
       <c r="C88">
-        <v>-3711.253770007891</v>
+        <v>-3824.753471934855</v>
       </c>
       <c r="D88">
-        <v>3633.788229992108</v>
+        <v>3606.885528065145</v>
       </c>
       <c r="E88">
-        <v>5899.541999999999</v>
+        <v>5986.138999999999</v>
       </c>
       <c r="F88">
-        <v>7447.341999999999</v>
+        <v>7533.938999999999</v>
       </c>
       <c r="G88">
         <v>102.3</v>
@@ -8503,37 +8503,37 @@
         <v>336.1000000000001</v>
       </c>
       <c r="M88">
-        <v>1495.4262736</v>
+        <v>1512.8149512</v>
       </c>
       <c r="N88">
-        <v>-1159.3262736</v>
+        <v>-1176.7149512</v>
       </c>
       <c r="O88">
-        <v>-370.9844075519999</v>
+        <v>-376.548784384</v>
       </c>
       <c r="P88">
-        <v>-788.3418660479997</v>
+        <v>-800.1661668159999</v>
       </c>
       <c r="Q88">
-        <v>591.4581339520003</v>
+        <v>579.6338331840001</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.3197111839592899</v>
+        <v>0.3407812750330814</v>
       </c>
       <c r="T88">
-        <v>3.569980959851989</v>
+        <v>3.844594879840603</v>
       </c>
       <c r="U88">
         <v>0.2008</v>
       </c>
       <c r="V88">
-        <v>0.07192063019000315</v>
+        <v>0.0710939562797732</v>
       </c>
       <c r="W88">
-        <v>0.1863583374578474</v>
+        <v>0.1865243335790215</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.2247519693437598</v>
+        <v>0.2221686133742913</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2065777359680493</v>
+        <v>0.2081277359680493</v>
       </c>
       <c r="C89">
-        <v>-3824.753471934855</v>
+        <v>-3937.857753770677</v>
       </c>
       <c r="D89">
-        <v>3606.885528065145</v>
+        <v>3580.378246229322</v>
       </c>
       <c r="E89">
-        <v>5986.138999999999</v>
+        <v>6072.735999999999</v>
       </c>
       <c r="F89">
-        <v>7533.938999999999</v>
+        <v>7620.535999999999</v>
       </c>
       <c r="G89">
         <v>102.3</v>
@@ -8585,37 +8585,37 @@
         <v>336.1000000000001</v>
       </c>
       <c r="M89">
-        <v>1512.8149512</v>
+        <v>1530.2036288</v>
       </c>
       <c r="N89">
-        <v>-1176.7149512</v>
+        <v>-1194.1036288</v>
       </c>
       <c r="O89">
-        <v>-376.548784384</v>
+        <v>-382.1131612159999</v>
       </c>
       <c r="P89">
-        <v>-800.1661668159999</v>
+        <v>-811.9904675839998</v>
       </c>
       <c r="Q89">
-        <v>579.6338331840001</v>
+        <v>567.8095324160001</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.3407812750330814</v>
+        <v>0.3653630479525048</v>
       </c>
       <c r="T89">
-        <v>3.844594879840603</v>
+        <v>4.164977786493987</v>
       </c>
       <c r="U89">
         <v>0.2008</v>
       </c>
       <c r="V89">
-        <v>0.0710939562797732</v>
+        <v>0.0702860704129576</v>
       </c>
       <c r="W89">
-        <v>0.1865243335790215</v>
+        <v>0.1866865570610781</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.2221686133742913</v>
+        <v>0.2196439700404925</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2081277359680493</v>
+        <v>0.2096777359680493</v>
       </c>
       <c r="C90">
-        <v>-3937.857753770677</v>
+        <v>-4050.575269832973</v>
       </c>
       <c r="D90">
-        <v>3580.378246229322</v>
+        <v>3554.257730167026</v>
       </c>
       <c r="E90">
-        <v>6072.735999999999</v>
+        <v>6159.332999999999</v>
       </c>
       <c r="F90">
-        <v>7620.535999999999</v>
+        <v>7707.132999999999</v>
       </c>
       <c r="G90">
         <v>102.3</v>
@@ -8667,37 +8667,37 @@
         <v>336.1000000000001</v>
       </c>
       <c r="M90">
-        <v>1530.2036288</v>
+        <v>1547.5923064</v>
       </c>
       <c r="N90">
-        <v>-1194.1036288</v>
+        <v>-1211.4923064</v>
       </c>
       <c r="O90">
-        <v>-382.1131612159999</v>
+        <v>-387.6775380479999</v>
       </c>
       <c r="P90">
-        <v>-811.9904675839998</v>
+        <v>-823.8147683519999</v>
       </c>
       <c r="Q90">
-        <v>567.8095324160001</v>
+        <v>555.9852316480001</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.3653630479525048</v>
+        <v>0.3944142341300054</v>
       </c>
       <c r="T90">
-        <v>4.164977786493987</v>
+        <v>4.543612130720714</v>
       </c>
       <c r="U90">
         <v>0.2008</v>
       </c>
       <c r="V90">
-        <v>0.0702860704129576</v>
+        <v>0.06949633928472214</v>
       </c>
       <c r="W90">
-        <v>0.1866865570610781</v>
+        <v>0.1868451350716278</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.2196439700404925</v>
+        <v>0.2171760602647567</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2096777359680493</v>
+        <v>0.2112277359680493</v>
       </c>
       <c r="C91">
-        <v>-4050.575269832973</v>
+        <v>-4162.91442371947</v>
       </c>
       <c r="D91">
-        <v>3554.257730167026</v>
+        <v>3528.51557628053</v>
       </c>
       <c r="E91">
-        <v>6159.332999999999</v>
+        <v>6245.929999999999</v>
       </c>
       <c r="F91">
-        <v>7707.132999999999</v>
+        <v>7793.73</v>
       </c>
       <c r="G91">
         <v>102.3</v>
@@ -8749,37 +8749,37 @@
         <v>336.1000000000001</v>
       </c>
       <c r="M91">
-        <v>1547.5923064</v>
+        <v>1564.980984</v>
       </c>
       <c r="N91">
-        <v>-1211.4923064</v>
+        <v>-1228.880984</v>
       </c>
       <c r="O91">
-        <v>-387.6775380479999</v>
+        <v>-393.24191488</v>
       </c>
       <c r="P91">
-        <v>-823.8147683519999</v>
+        <v>-835.6390691199999</v>
       </c>
       <c r="Q91">
-        <v>555.9852316480001</v>
+        <v>544.16093088</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.3944142341300054</v>
+        <v>0.4292756575430059</v>
       </c>
       <c r="T91">
-        <v>4.543612130720714</v>
+        <v>4.997973343792785</v>
       </c>
       <c r="U91">
         <v>0.2008</v>
       </c>
       <c r="V91">
-        <v>0.06949633928472214</v>
+        <v>0.06872415773711411</v>
       </c>
       <c r="W91">
-        <v>0.1868451350716278</v>
+        <v>0.1870001891263875</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.2171760602647567</v>
+        <v>0.2147629929284816</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2112277359680493</v>
+        <v>0.2127777359680493</v>
       </c>
       <c r="C92">
-        <v>-4162.91442371947</v>
+        <v>-4274.883377322067</v>
       </c>
       <c r="D92">
-        <v>3528.51557628053</v>
+        <v>3503.143622677932</v>
       </c>
       <c r="E92">
-        <v>6245.929999999999</v>
+        <v>6332.526999999999</v>
       </c>
       <c r="F92">
-        <v>7793.73</v>
+        <v>7880.326999999999</v>
       </c>
       <c r="G92">
         <v>102.3</v>
@@ -8831,37 +8831,37 @@
         <v>336.1000000000001</v>
       </c>
       <c r="M92">
-        <v>1564.980984</v>
+        <v>1582.3696616</v>
       </c>
       <c r="N92">
-        <v>-1228.880984</v>
+        <v>-1246.2696616</v>
       </c>
       <c r="O92">
-        <v>-393.24191488</v>
+        <v>-398.806291712</v>
       </c>
       <c r="P92">
-        <v>-835.6390691199999</v>
+        <v>-847.4633698879999</v>
       </c>
       <c r="Q92">
-        <v>544.16093088</v>
+        <v>532.3366301120001</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.4292756575430059</v>
+        <v>0.4718840639366733</v>
       </c>
       <c r="T92">
-        <v>4.997973343792785</v>
+        <v>5.553303715325318</v>
       </c>
       <c r="U92">
         <v>0.2008</v>
       </c>
       <c r="V92">
-        <v>0.06872415773711411</v>
+        <v>0.06796894721253043</v>
       </c>
       <c r="W92">
-        <v>0.1870001891263875</v>
+        <v>0.1871518353997239</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.2147629929284816</v>
+        <v>0.2124029600391576</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2127777359680493</v>
+        <v>0.2143277359680493</v>
       </c>
       <c r="C93">
-        <v>-4274.883377322067</v>
+        <v>-4386.490059454788</v>
       </c>
       <c r="D93">
-        <v>3503.143622677932</v>
+        <v>3478.133940545211</v>
       </c>
       <c r="E93">
-        <v>6332.526999999999</v>
+        <v>6419.123999999999</v>
       </c>
       <c r="F93">
-        <v>7880.326999999999</v>
+        <v>7966.923999999999</v>
       </c>
       <c r="G93">
         <v>102.3</v>
@@ -8913,37 +8913,37 @@
         <v>336.1000000000001</v>
       </c>
       <c r="M93">
-        <v>1582.3696616</v>
+        <v>1599.7583392</v>
       </c>
       <c r="N93">
-        <v>-1246.2696616</v>
+        <v>-1263.6583392</v>
       </c>
       <c r="O93">
-        <v>-398.806291712</v>
+        <v>-404.370668544</v>
       </c>
       <c r="P93">
-        <v>-847.4633698879999</v>
+        <v>-859.2876706559998</v>
       </c>
       <c r="Q93">
-        <v>532.3366301120001</v>
+        <v>520.5123293440001</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.4718840639366733</v>
+        <v>0.5251445719287575</v>
       </c>
       <c r="T93">
-        <v>5.553303715325318</v>
+        <v>6.247466679740984</v>
       </c>
       <c r="U93">
         <v>0.2008</v>
       </c>
       <c r="V93">
-        <v>0.06796894721253043</v>
+        <v>0.06723015430804641</v>
       </c>
       <c r="W93">
-        <v>0.1871518353997239</v>
+        <v>0.1873001850149443</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.2124029600391576</v>
+        <v>0.210094232212645</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2143277359680493</v>
+        <v>0.2158777359680493</v>
       </c>
       <c r="C94">
-        <v>-4386.490059454788</v>
+        <v>-4497.74217411476</v>
       </c>
       <c r="D94">
-        <v>3478.133940545211</v>
+        <v>3453.47882588524</v>
       </c>
       <c r="E94">
-        <v>6419.123999999999</v>
+        <v>6505.721</v>
       </c>
       <c r="F94">
-        <v>7966.923999999999</v>
+        <v>8053.521</v>
       </c>
       <c r="G94">
         <v>102.3</v>
@@ -8995,37 +8995,37 @@
         <v>336.1000000000001</v>
       </c>
       <c r="M94">
-        <v>1599.7583392</v>
+        <v>1617.1470168</v>
       </c>
       <c r="N94">
-        <v>-1263.6583392</v>
+        <v>-1281.0470168</v>
       </c>
       <c r="O94">
-        <v>-404.370668544</v>
+        <v>-409.935045376</v>
       </c>
       <c r="P94">
-        <v>-859.2876706559998</v>
+        <v>-871.1119714239999</v>
       </c>
       <c r="Q94">
-        <v>520.5123293440001</v>
+        <v>508.6880285760001</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.5251445719287575</v>
+        <v>0.59362236791858</v>
       </c>
       <c r="T94">
-        <v>6.247466679740984</v>
+        <v>7.139961919703982</v>
       </c>
       <c r="U94">
         <v>0.2008</v>
       </c>
       <c r="V94">
-        <v>0.06723015430804641</v>
+        <v>0.06650724942301364</v>
       </c>
       <c r="W94">
-        <v>0.1873001850149443</v>
+        <v>0.1874453443158589</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.210094232212645</v>
+        <v>0.2078351544469177</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2158777359680493</v>
+        <v>0.2174277359680493</v>
       </c>
       <c r="C95">
-        <v>-4497.74217411476</v>
+        <v>-4608.647208394317</v>
       </c>
       <c r="D95">
-        <v>3453.47882588524</v>
+        <v>3429.170791605682</v>
       </c>
       <c r="E95">
-        <v>6505.721</v>
+        <v>6592.317999999999</v>
       </c>
       <c r="F95">
-        <v>8053.521</v>
+        <v>8140.117999999999</v>
       </c>
       <c r="G95">
         <v>102.3</v>
@@ -9077,37 +9077,37 @@
         <v>336.1000000000001</v>
       </c>
       <c r="M95">
-        <v>1617.1470168</v>
+        <v>1634.5356944</v>
       </c>
       <c r="N95">
-        <v>-1281.0470168</v>
+        <v>-1298.4356944</v>
       </c>
       <c r="O95">
-        <v>-409.935045376</v>
+        <v>-415.4994222079999</v>
       </c>
       <c r="P95">
-        <v>-871.1119714239999</v>
+        <v>-882.9362721919999</v>
       </c>
       <c r="Q95">
-        <v>508.6880285760001</v>
+        <v>496.863727808</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.59362236791858</v>
+        <v>0.6849260959050102</v>
       </c>
       <c r="T95">
-        <v>7.139961919703982</v>
+        <v>8.329955572987981</v>
       </c>
       <c r="U95">
         <v>0.2008</v>
       </c>
       <c r="V95">
-        <v>0.06650724942301364</v>
+        <v>0.06579972549298159</v>
       </c>
       <c r="W95">
-        <v>0.1874453443158589</v>
+        <v>0.1875874151210093</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.2078351544469177</v>
+        <v>0.2056241421655675</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2174277359680493</v>
+        <v>0.2189777359680493</v>
       </c>
       <c r="C96">
-        <v>-4608.647208394317</v>
+        <v>-4719.212440061297</v>
       </c>
       <c r="D96">
-        <v>3429.170791605682</v>
+        <v>3405.202559938703</v>
       </c>
       <c r="E96">
-        <v>6592.317999999999</v>
+        <v>6678.915</v>
       </c>
       <c r="F96">
-        <v>8140.117999999999</v>
+        <v>8226.715</v>
       </c>
       <c r="G96">
         <v>102.3</v>
@@ -9159,37 +9159,37 @@
         <v>336.1000000000001</v>
       </c>
       <c r="M96">
-        <v>1634.5356944</v>
+        <v>1651.924372</v>
       </c>
       <c r="N96">
-        <v>-1298.4356944</v>
+        <v>-1315.824372</v>
       </c>
       <c r="O96">
-        <v>-415.4994222079999</v>
+        <v>-421.06379904</v>
       </c>
       <c r="P96">
-        <v>-882.9362721919999</v>
+        <v>-894.76057296</v>
       </c>
       <c r="Q96">
-        <v>496.863727808</v>
+        <v>485.03942704</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.6849260959050102</v>
+        <v>0.8127513150860127</v>
       </c>
       <c r="T96">
-        <v>8.329955572987981</v>
+        <v>9.995946687585583</v>
       </c>
       <c r="U96">
         <v>0.2008</v>
       </c>
       <c r="V96">
-        <v>0.06579972549298159</v>
+        <v>0.06510709680358177</v>
       </c>
       <c r="W96">
-        <v>0.1875874151210093</v>
+        <v>0.1877264949618408</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.2056241421655675</v>
+        <v>0.2034596775111931</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2189777359680493</v>
+        <v>0.2205277359680493</v>
       </c>
       <c r="C97">
-        <v>-4719.212440061297</v>
+        <v>-4829.444944823643</v>
       </c>
       <c r="D97">
-        <v>3405.202559938703</v>
+        <v>3381.567055176356</v>
       </c>
       <c r="E97">
-        <v>6678.915</v>
+        <v>6765.512</v>
       </c>
       <c r="F97">
-        <v>8226.715</v>
+        <v>8313.312</v>
       </c>
       <c r="G97">
         <v>102.3</v>
@@ -9241,37 +9241,37 @@
         <v>336.1000000000001</v>
       </c>
       <c r="M97">
-        <v>1651.924372</v>
+        <v>1669.3130496</v>
       </c>
       <c r="N97">
-        <v>-1315.824372</v>
+        <v>-1333.2130496</v>
       </c>
       <c r="O97">
-        <v>-421.06379904</v>
+        <v>-426.628175872</v>
       </c>
       <c r="P97">
-        <v>-894.76057296</v>
+        <v>-906.584873728</v>
       </c>
       <c r="Q97">
-        <v>485.03942704</v>
+        <v>473.2151262719999</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.8127513150860127</v>
+        <v>1.004489143857516</v>
       </c>
       <c r="T97">
-        <v>9.995946687585583</v>
+        <v>12.49493335948198</v>
       </c>
       <c r="U97">
         <v>0.2008</v>
       </c>
       <c r="V97">
-        <v>0.06510709680358177</v>
+        <v>0.06442889787854447</v>
       </c>
       <c r="W97">
-        <v>0.1877264949618408</v>
+        <v>0.1878626773059883</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.2034596775111931</v>
+        <v>0.2013403058704515</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2205277359680493</v>
+        <v>0.2564030048067588</v>
       </c>
       <c r="C98">
-        <v>-4829.444944823641</v>
+        <v>-5384.101891179167</v>
       </c>
       <c r="D98">
-        <v>3381.567055176357</v>
+        <v>2913.507108820831</v>
       </c>
       <c r="E98">
-        <v>6765.511999999998</v>
+        <v>6852.108999999998</v>
       </c>
       <c r="F98">
-        <v>8313.311999999998</v>
+        <v>8399.908999999998</v>
       </c>
       <c r="G98">
         <v>102.3</v>
@@ -9323,45 +9323,45 @@
         <v>336.1000000000001</v>
       </c>
       <c r="M98">
-        <v>1669.3130496</v>
+        <v>1980.6985422</v>
       </c>
       <c r="N98">
-        <v>-1333.2130496</v>
+        <v>-1644.598542199999</v>
       </c>
       <c r="O98">
-        <v>-426.6281758719999</v>
+        <v>-526.2715335039999</v>
       </c>
       <c r="P98">
-        <v>-906.5848737279996</v>
+        <v>-1118.327008696</v>
       </c>
       <c r="Q98">
-        <v>473.2151262720004</v>
+        <v>261.4729913040003</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.004489143857514</v>
+        <v>1.336561153100335</v>
       </c>
       <c r="T98">
-        <v>12.49493335948195</v>
+        <v>16.82294484539798</v>
       </c>
       <c r="U98">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.06442889787854449</v>
+        <v>0.05430003491623717</v>
       </c>
       <c r="W98">
-        <v>0.1878626773059883</v>
+        <v>0.2229960517667513</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y98">
-        <v>0.2013403058704515</v>
+        <v>0.1696876091132412</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2564030048067588</v>
+        <v>0.2583030048067588</v>
       </c>
       <c r="C99">
-        <v>-5384.101891179167</v>
+        <v>-5491.901336376286</v>
       </c>
       <c r="D99">
-        <v>2913.507108820831</v>
+        <v>2892.304663623713</v>
       </c>
       <c r="E99">
-        <v>6852.108999999998</v>
+        <v>6938.705999999999</v>
       </c>
       <c r="F99">
-        <v>8399.908999999998</v>
+        <v>8486.505999999999</v>
       </c>
       <c r="G99">
         <v>102.3</v>
@@ -9405,37 +9405,37 @@
         <v>336.1000000000001</v>
       </c>
       <c r="M99">
-        <v>1980.6985422</v>
+        <v>2001.1181148</v>
       </c>
       <c r="N99">
-        <v>-1644.598542199999</v>
+        <v>-1665.0181148</v>
       </c>
       <c r="O99">
-        <v>-526.2715335039999</v>
+        <v>-532.8057967359999</v>
       </c>
       <c r="P99">
-        <v>-1118.327008696</v>
+        <v>-1132.212318064</v>
       </c>
       <c r="Q99">
-        <v>261.4729913040003</v>
+        <v>247.5876819360003</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.336561153100335</v>
+        <v>1.981941729650502</v>
       </c>
       <c r="T99">
-        <v>16.82294484539798</v>
+        <v>25.23441726809697</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.05430003491623717</v>
+        <v>0.05374595292729598</v>
       </c>
       <c r="W99">
-        <v>0.2229960517667513</v>
+        <v>0.2231267042997436</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.1696876091132412</v>
+        <v>0.1679561028977999</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2583030048067588</v>
+        <v>0.2602030048067588</v>
       </c>
       <c r="C100">
-        <v>-5491.901336376286</v>
+        <v>-5599.394418252565</v>
       </c>
       <c r="D100">
-        <v>2892.304663623713</v>
+        <v>2871.408581747434</v>
       </c>
       <c r="E100">
-        <v>6938.705999999999</v>
+        <v>7025.302999999999</v>
       </c>
       <c r="F100">
-        <v>8486.505999999999</v>
+        <v>8573.102999999999</v>
       </c>
       <c r="G100">
         <v>102.3</v>
@@ -9487,37 +9487,37 @@
         <v>336.1000000000001</v>
       </c>
       <c r="M100">
-        <v>2001.1181148</v>
+        <v>2021.5376874</v>
       </c>
       <c r="N100">
-        <v>-1665.0181148</v>
+        <v>-1685.4376874</v>
       </c>
       <c r="O100">
-        <v>-532.8057967359999</v>
+        <v>-539.3400599679999</v>
       </c>
       <c r="P100">
-        <v>-1132.212318064</v>
+        <v>-1146.097627432</v>
       </c>
       <c r="Q100">
-        <v>247.5876819360003</v>
+        <v>233.7023725680001</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.981941729650502</v>
+        <v>3.918083459301005</v>
       </c>
       <c r="T100">
-        <v>25.23441726809697</v>
+        <v>50.46883453619395</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.05374595292729598</v>
+        <v>0.05320306451388894</v>
       </c>
       <c r="W100">
-        <v>0.2231267042997436</v>
+        <v>0.223254717387625</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.1679561028977999</v>
+        <v>0.166259576605903</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2602030048067588</v>
-      </c>
-      <c r="C101">
-        <v>-5599.394418252565</v>
-      </c>
-      <c r="D101">
-        <v>2871.408581747434</v>
-      </c>
-      <c r="E101">
-        <v>7025.302999999999</v>
-      </c>
-      <c r="F101">
-        <v>8573.102999999999</v>
-      </c>
-      <c r="G101">
-        <v>102.3</v>
-      </c>
-      <c r="H101">
-        <v>7111.9</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>1715.9</v>
-      </c>
-      <c r="K101">
-        <v>1379.8</v>
-      </c>
-      <c r="L101">
-        <v>336.1000000000001</v>
-      </c>
-      <c r="M101">
-        <v>2021.5376874</v>
-      </c>
-      <c r="N101">
-        <v>-1685.4376874</v>
-      </c>
-      <c r="O101">
-        <v>-539.3400599679999</v>
-      </c>
-      <c r="P101">
-        <v>-1146.097627432</v>
-      </c>
-      <c r="Q101">
-        <v>233.7023725680001</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>3.918083459301005</v>
-      </c>
-      <c r="T101">
-        <v>50.46883453619395</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.05320306451388894</v>
-      </c>
-      <c r="W101">
-        <v>0.223254717387625</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.166259576605903</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
